--- a/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_검사기팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_검사기팀_입력_2026.xlsx
@@ -183,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -315,6 +315,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -915,7 +924,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="53" t="inlineStr">
+      <c r="A1" s="56" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 검사기팀 │ 2026</t>
         </is>
@@ -939,7 +948,7 @@
       <c r="R1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="54" t="inlineStr">
+      <c r="A2" s="57" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 검사기팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -960,9 +969,9 @@
       <c r="O2" s="16" t="n"/>
       <c r="P2" s="16" t="n"/>
       <c r="Q2" s="17" t="n"/>
-      <c r="R2" s="55" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-02 01:43</t>
+      <c r="R2" s="58" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 00:44</t>
         </is>
       </c>
     </row>

--- a/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_검사기팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_검사기팀_입력_2026.xlsx
@@ -183,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -315,6 +315,24 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -551,8 +569,11 @@
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 담당자
-(직접 입력)</t>
+        <t>▣ 부서 담당자
+• 부서 내 실제 담당자 이름 입력
+  예: 정민규, 한재운, 이찬
+• 입력 시: PMS에도 자동 반영
+• 빈 칸: 부서 참여 확정, 담당자 미정</t>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
@@ -566,44 +587,79 @@
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 검토
-(직접 입력)</t>
+        <t>▣ 검토 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <t>▣ PCB
-(직접 입력)</t>
+        <t>▣ PCB (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <t>▣ H/W
-(직접 입력)</t>
+        <t>▣ H/W (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>▣ F/W
-(직접 입력)</t>
+        <t>▣ F/W (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 동작검증
-(직접 입력)</t>
+        <t>▣ 동작검증 (세부항목 진척률)
+★ 진척률 % 입력 (날짜 아님 ⚠️)
+• 0~1 사이 소수로 입력
+  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
+• 0 또는 빈 칸 = 미착수
+• 부서장·담당자가 매주 진척률 갱신
+• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 상태
-(직접 입력)</t>
+        <t>▣ 부서 작업 상태
+• 드롭다운 선택:
+  미착수 — 작업 시작 안 함
+  진행중 — 작업 진행 중
+  완료   — 부서 작업 완료
+  N/A    — 해당 부서 무관 프로젝트
+• 부서장이 매주 상태 갱신 권장</t>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 메모
-(직접 입력)</t>
+        <t>▣ 메모 (부서 자유 입력)
+• 자유 텍스트 입력
+• 활용:
+  - 이슈사항 (예: 자재 결품, 외주 지연)
+  - 변경 요청 (예: 사양 변경, 납기 조정)
+  - 다른 부서·PM에게 공유할 정보
+• 대시보드 집계에는 미포함</t>
       </text>
     </comment>
   </commentList>
@@ -924,7 +980,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="56" t="inlineStr">
+      <c r="A1" s="62" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 검사기팀 │ 2026</t>
         </is>
@@ -948,7 +1004,7 @@
       <c r="R1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="57" t="inlineStr">
+      <c r="A2" s="63" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 검사기팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -969,9 +1025,9 @@
       <c r="O2" s="16" t="n"/>
       <c r="P2" s="16" t="n"/>
       <c r="Q2" s="17" t="n"/>
-      <c r="R2" s="58" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 00:44</t>
+      <c r="R2" s="64" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 01:06</t>
         </is>
       </c>
     </row>

--- a/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_검사기팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_검사기팀_입력_2026.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -59,8 +59,20 @@
       <color rgb="00FFFFFF"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="002E7D32"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00E65100"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -112,8 +124,13 @@
         <fgColor rgb="008B1E22"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B08F36"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -179,11 +196,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -351,6 +382,57 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -587,60 +669,32 @@
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 검토 (세부항목 진척률)
-★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        <t>▣ 부서 시작일
+★ 날짜 입력 (% 아님 ⚠️)
+• 형식: YYYY-MM-DD  예: 2026-05-10
+• 허용: 26-5-10, 260510, 2026.5.10 (자동 정규화)
+• 부서가 ★실제로 작업을 시작한 날짜★ 기입
+• PO 후 작업 착수일 (지시 받은 날 아님)
+• 비워두면: 미착수 상태
+• v3.1 검사기 운영: 진척률 % 대신 시작·완료일로 추적
+  (2주 단위 빠른 작업 사이클이라 % 입력이 비효율)</t>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <t>▣ PCB (세부항목 진척률)
-★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
+        <t>▣ 부서 완료일
+★ 날짜 입력 (% 아님 ⚠️)
+• 형식: YYYY-MM-DD  예: 2026-05-24
+• 허용: 26-5-24, 260524, 2026.5.24 (자동 정규화)
+• 부서 작업이 ★실제로 완료된 날짜★ 기입
+• 예정일 아닌 ★실제 완료일★ 만 입력
+• 비워두면: PMS 진행현황에서 '미완료'로 집계
+• 입력 시: PMS 2_진행현황에 자동 표시 +
+  전체 진척률 = (완료 부서 수) / (참여 부서 수) 자동 계산
+• '제외' 부서는 분모에서 제외됨</t>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
-      <text>
-        <t>▣ H/W (세부항목 진척률)
-★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
-      </text>
-    </comment>
-    <comment ref="O4" authorId="0" shapeId="0">
-      <text>
-        <t>▣ F/W (세부항목 진척률)
-★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
-      </text>
-    </comment>
-    <comment ref="P4" authorId="0" shapeId="0">
-      <text>
-        <t>▣ 동작검증 (세부항목 진척률)
-★ 진척률 % 입력 (날짜 아님 ⚠️)
-• 0~1 사이 소수로 입력
-  예: 0.5 = 50%, 0.8 = 80%, 1.0 = 100%
-• 0 또는 빈 칸 = 미착수
-• 부서장·담당자가 매주 진척률 갱신
-• 전체진척률(%)은 세부항목 평균으로 자동 계산</t>
-      </text>
-    </comment>
-    <comment ref="Q4" authorId="0" shapeId="0">
       <text>
         <t>▣ 부서 작업 상태
 • 드롭다운 선택:
@@ -651,7 +705,7 @@
 • 부서장이 매주 상태 갱신 권장</t>
       </text>
     </comment>
-    <comment ref="R4" authorId="0" shapeId="0">
+    <comment ref="O4" authorId="0" shapeId="0">
       <text>
         <t>▣ 메모 (부서 자유 입력)
 • 자유 텍스트 입력
@@ -956,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R140"/>
+  <dimension ref="A1:O140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -970,17 +1024,17 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" style="43" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="6" customWidth="1" style="43" min="12" max="12"/>
-    <col width="5" customWidth="1" style="43" min="13" max="13"/>
-    <col width="5" customWidth="1" style="43" min="14" max="14"/>
-    <col width="5" customWidth="1" style="43" min="15" max="15"/>
+    <col width="12" customWidth="1" style="43" min="12" max="12"/>
+    <col width="12" customWidth="1" style="43" min="13" max="13"/>
+    <col width="10" customWidth="1" style="43" min="14" max="14"/>
+    <col width="28" customWidth="1" style="43" min="15" max="15"/>
     <col width="10" customWidth="1" style="43" min="16" max="16"/>
     <col width="10" customWidth="1" style="43" min="17" max="17"/>
     <col width="28" customWidth="1" style="43" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="62" t="inlineStr">
+      <c r="A1" s="79" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 검사기팀 │ 2026</t>
         </is>
@@ -998,13 +1052,10 @@
       <c r="L1" s="16" t="n"/>
       <c r="M1" s="16" t="n"/>
       <c r="N1" s="16" t="n"/>
-      <c r="O1" s="16" t="n"/>
-      <c r="P1" s="16" t="n"/>
-      <c r="Q1" s="16" t="n"/>
-      <c r="R1" s="17" t="n"/>
+      <c r="O1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="63" t="inlineStr">
+      <c r="A2" s="80" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 검사기팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1021,13 +1072,10 @@
       <c r="K2" s="16" t="n"/>
       <c r="L2" s="16" t="n"/>
       <c r="M2" s="16" t="n"/>
-      <c r="N2" s="16" t="n"/>
-      <c r="O2" s="16" t="n"/>
-      <c r="P2" s="16" t="n"/>
-      <c r="Q2" s="17" t="n"/>
-      <c r="R2" s="64" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 01:06</t>
+      <c r="N2" s="17" t="n"/>
+      <c r="O2" s="81" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 02:00</t>
         </is>
       </c>
     </row>
@@ -1087,37 +1135,22 @@
           <t>🔒자동</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>✏입력</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>✏입력</t>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>PO후입력</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>PO후입력</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>✏입력</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>✏입력</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="inlineStr">
-        <is>
-          <t>✏입력</t>
-        </is>
-      </c>
-      <c r="Q3" s="3" t="inlineStr">
-        <is>
           <t>✏선택▼</t>
         </is>
       </c>
-      <c r="R3" s="4" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t>✏메모</t>
         </is>
@@ -1179,37 +1212,24 @@
           <t>전체진척률(%)</t>
         </is>
       </c>
-      <c r="L4" s="7" t="inlineStr">
-        <is>
-          <t>검토</t>
-        </is>
-      </c>
-      <c r="M4" s="7" t="inlineStr">
-        <is>
-          <t>PCB</t>
+      <c r="L4" s="72" t="inlineStr">
+        <is>
+          <t>부서
+시작일</t>
+        </is>
+      </c>
+      <c r="M4" s="72" t="inlineStr">
+        <is>
+          <t>부서
+완료일</t>
         </is>
       </c>
       <c r="N4" s="7" t="inlineStr">
         <is>
-          <t>H/W</t>
+          <t>상태</t>
         </is>
       </c>
       <c r="O4" s="7" t="inlineStr">
-        <is>
-          <t>F/W</t>
-        </is>
-      </c>
-      <c r="P4" s="7" t="inlineStr">
-        <is>
-          <t>동작검증</t>
-        </is>
-      </c>
-      <c r="Q4" s="7" t="inlineStr">
-        <is>
-          <t>상태</t>
-        </is>
-      </c>
-      <c r="R4" s="7" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
@@ -1261,13 +1281,10 @@
       </c>
       <c r="J5" s="9" t="n"/>
       <c r="K5" s="10" t="inlineStr"/>
-      <c r="L5" s="11" t="n"/>
-      <c r="M5" s="11" t="n"/>
-      <c r="N5" s="11" t="n"/>
-      <c r="O5" s="11" t="n"/>
-      <c r="P5" s="11" t="n"/>
-      <c r="Q5" s="9" t="n"/>
-      <c r="R5" s="22" t="n"/>
+      <c r="L5" s="9" t="n"/>
+      <c r="M5" s="9" t="n"/>
+      <c r="N5" s="9" t="n"/>
+      <c r="O5" s="22" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="12" t="n">
@@ -1315,13 +1332,10 @@
       </c>
       <c r="J6" s="13" t="n"/>
       <c r="K6" s="14" t="inlineStr"/>
-      <c r="L6" s="15" t="n"/>
-      <c r="M6" s="15" t="n"/>
-      <c r="N6" s="15" t="n"/>
-      <c r="O6" s="15" t="n"/>
-      <c r="P6" s="15" t="n"/>
-      <c r="Q6" s="13" t="n"/>
-      <c r="R6" s="24" t="n"/>
+      <c r="L6" s="13" t="n"/>
+      <c r="M6" s="13" t="n"/>
+      <c r="N6" s="13" t="n"/>
+      <c r="O6" s="24" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="8" t="n">
@@ -1369,13 +1383,10 @@
       </c>
       <c r="J7" s="9" t="n"/>
       <c r="K7" s="10" t="inlineStr"/>
-      <c r="L7" s="11" t="n"/>
-      <c r="M7" s="11" t="n"/>
-      <c r="N7" s="11" t="n"/>
-      <c r="O7" s="11" t="n"/>
-      <c r="P7" s="11" t="n"/>
-      <c r="Q7" s="9" t="n"/>
-      <c r="R7" s="22" t="n"/>
+      <c r="L7" s="9" t="n"/>
+      <c r="M7" s="9" t="n"/>
+      <c r="N7" s="9" t="n"/>
+      <c r="O7" s="22" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="12" t="n">
@@ -1423,13 +1434,10 @@
       </c>
       <c r="J8" s="13" t="n"/>
       <c r="K8" s="14" t="inlineStr"/>
-      <c r="L8" s="15" t="n"/>
-      <c r="M8" s="15" t="n"/>
-      <c r="N8" s="15" t="n"/>
-      <c r="O8" s="15" t="n"/>
-      <c r="P8" s="15" t="n"/>
-      <c r="Q8" s="13" t="n"/>
-      <c r="R8" s="24" t="n"/>
+      <c r="L8" s="13" t="n"/>
+      <c r="M8" s="13" t="n"/>
+      <c r="N8" s="13" t="n"/>
+      <c r="O8" s="24" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="8" t="n">
@@ -1477,13 +1485,10 @@
       </c>
       <c r="J9" s="9" t="n"/>
       <c r="K9" s="10" t="inlineStr"/>
-      <c r="L9" s="11" t="n"/>
-      <c r="M9" s="11" t="n"/>
-      <c r="N9" s="11" t="n"/>
-      <c r="O9" s="11" t="n"/>
-      <c r="P9" s="11" t="n"/>
-      <c r="Q9" s="9" t="n"/>
-      <c r="R9" s="22" t="n"/>
+      <c r="L9" s="9" t="n"/>
+      <c r="M9" s="9" t="n"/>
+      <c r="N9" s="9" t="n"/>
+      <c r="O9" s="22" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="12" t="n">
@@ -1531,13 +1536,10 @@
       </c>
       <c r="J10" s="13" t="n"/>
       <c r="K10" s="14" t="inlineStr"/>
-      <c r="L10" s="15" t="n"/>
-      <c r="M10" s="15" t="n"/>
-      <c r="N10" s="15" t="n"/>
-      <c r="O10" s="15" t="n"/>
-      <c r="P10" s="15" t="n"/>
-      <c r="Q10" s="13" t="n"/>
-      <c r="R10" s="24" t="n"/>
+      <c r="L10" s="13" t="n"/>
+      <c r="M10" s="13" t="n"/>
+      <c r="N10" s="13" t="n"/>
+      <c r="O10" s="24" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="8" t="n">
@@ -1585,13 +1587,10 @@
       </c>
       <c r="J11" s="9" t="n"/>
       <c r="K11" s="10" t="inlineStr"/>
-      <c r="L11" s="11" t="n"/>
-      <c r="M11" s="11" t="n"/>
-      <c r="N11" s="11" t="n"/>
-      <c r="O11" s="11" t="n"/>
-      <c r="P11" s="11" t="n"/>
-      <c r="Q11" s="9" t="n"/>
-      <c r="R11" s="22" t="n"/>
+      <c r="L11" s="9" t="n"/>
+      <c r="M11" s="9" t="n"/>
+      <c r="N11" s="9" t="n"/>
+      <c r="O11" s="22" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="12" t="n">
@@ -1639,13 +1638,10 @@
       </c>
       <c r="J12" s="13" t="n"/>
       <c r="K12" s="14" t="inlineStr"/>
-      <c r="L12" s="15" t="n"/>
-      <c r="M12" s="15" t="n"/>
-      <c r="N12" s="15" t="n"/>
-      <c r="O12" s="15" t="n"/>
-      <c r="P12" s="15" t="n"/>
-      <c r="Q12" s="13" t="n"/>
-      <c r="R12" s="24" t="n"/>
+      <c r="L12" s="13" t="n"/>
+      <c r="M12" s="13" t="n"/>
+      <c r="N12" s="13" t="n"/>
+      <c r="O12" s="24" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="8" t="n">
@@ -1693,13 +1689,10 @@
       </c>
       <c r="J13" s="9" t="n"/>
       <c r="K13" s="10" t="inlineStr"/>
-      <c r="L13" s="11" t="n"/>
-      <c r="M13" s="11" t="n"/>
-      <c r="N13" s="11" t="n"/>
-      <c r="O13" s="11" t="n"/>
-      <c r="P13" s="11" t="n"/>
-      <c r="Q13" s="9" t="n"/>
-      <c r="R13" s="22" t="n"/>
+      <c r="L13" s="9" t="n"/>
+      <c r="M13" s="9" t="n"/>
+      <c r="N13" s="9" t="n"/>
+      <c r="O13" s="22" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="12" t="n">
@@ -1747,13 +1740,10 @@
       </c>
       <c r="J14" s="13" t="n"/>
       <c r="K14" s="14" t="inlineStr"/>
-      <c r="L14" s="15" t="n"/>
-      <c r="M14" s="15" t="n"/>
-      <c r="N14" s="15" t="n"/>
-      <c r="O14" s="15" t="n"/>
-      <c r="P14" s="15" t="n"/>
-      <c r="Q14" s="13" t="n"/>
-      <c r="R14" s="24" t="n"/>
+      <c r="L14" s="13" t="n"/>
+      <c r="M14" s="13" t="n"/>
+      <c r="N14" s="13" t="n"/>
+      <c r="O14" s="24" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="8" t="n">
@@ -1801,13 +1791,10 @@
       </c>
       <c r="J15" s="9" t="n"/>
       <c r="K15" s="10" t="inlineStr"/>
-      <c r="L15" s="11" t="n"/>
-      <c r="M15" s="11" t="n"/>
-      <c r="N15" s="11" t="n"/>
-      <c r="O15" s="11" t="n"/>
-      <c r="P15" s="11" t="n"/>
-      <c r="Q15" s="9" t="n"/>
-      <c r="R15" s="22" t="n"/>
+      <c r="L15" s="9" t="n"/>
+      <c r="M15" s="9" t="n"/>
+      <c r="N15" s="9" t="n"/>
+      <c r="O15" s="22" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="12" t="n">
@@ -1855,13 +1842,10 @@
       </c>
       <c r="J16" s="13" t="n"/>
       <c r="K16" s="14" t="inlineStr"/>
-      <c r="L16" s="15" t="n"/>
-      <c r="M16" s="15" t="n"/>
-      <c r="N16" s="15" t="n"/>
-      <c r="O16" s="15" t="n"/>
-      <c r="P16" s="15" t="n"/>
-      <c r="Q16" s="13" t="n"/>
-      <c r="R16" s="24" t="n"/>
+      <c r="L16" s="13" t="n"/>
+      <c r="M16" s="13" t="n"/>
+      <c r="N16" s="13" t="n"/>
+      <c r="O16" s="24" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="8" t="n">
@@ -1909,13 +1893,10 @@
       </c>
       <c r="J17" s="9" t="n"/>
       <c r="K17" s="10" t="inlineStr"/>
-      <c r="L17" s="11" t="n"/>
-      <c r="M17" s="11" t="n"/>
-      <c r="N17" s="11" t="n"/>
-      <c r="O17" s="11" t="n"/>
-      <c r="P17" s="11" t="n"/>
-      <c r="Q17" s="9" t="n"/>
-      <c r="R17" s="22" t="n"/>
+      <c r="L17" s="9" t="n"/>
+      <c r="M17" s="9" t="n"/>
+      <c r="N17" s="9" t="n"/>
+      <c r="O17" s="22" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="12" t="n">
@@ -1963,13 +1944,10 @@
       </c>
       <c r="J18" s="13" t="n"/>
       <c r="K18" s="14" t="inlineStr"/>
-      <c r="L18" s="15" t="n"/>
-      <c r="M18" s="15" t="n"/>
-      <c r="N18" s="15" t="n"/>
-      <c r="O18" s="15" t="n"/>
-      <c r="P18" s="15" t="n"/>
-      <c r="Q18" s="13" t="n"/>
-      <c r="R18" s="24" t="n"/>
+      <c r="L18" s="13" t="n"/>
+      <c r="M18" s="13" t="n"/>
+      <c r="N18" s="13" t="n"/>
+      <c r="O18" s="24" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="8" t="n">
@@ -2017,13 +1995,10 @@
       </c>
       <c r="J19" s="9" t="n"/>
       <c r="K19" s="10" t="inlineStr"/>
-      <c r="L19" s="11" t="n"/>
-      <c r="M19" s="11" t="n"/>
-      <c r="N19" s="11" t="n"/>
-      <c r="O19" s="11" t="n"/>
-      <c r="P19" s="11" t="n"/>
-      <c r="Q19" s="9" t="n"/>
-      <c r="R19" s="22" t="n"/>
+      <c r="L19" s="9" t="n"/>
+      <c r="M19" s="9" t="n"/>
+      <c r="N19" s="9" t="n"/>
+      <c r="O19" s="22" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="12" t="n">
@@ -2071,13 +2046,10 @@
       </c>
       <c r="J20" s="13" t="n"/>
       <c r="K20" s="14" t="inlineStr"/>
-      <c r="L20" s="15" t="n"/>
-      <c r="M20" s="15" t="n"/>
-      <c r="N20" s="15" t="n"/>
-      <c r="O20" s="15" t="n"/>
-      <c r="P20" s="15" t="n"/>
-      <c r="Q20" s="13" t="n"/>
-      <c r="R20" s="24" t="n"/>
+      <c r="L20" s="13" t="n"/>
+      <c r="M20" s="13" t="n"/>
+      <c r="N20" s="13" t="n"/>
+      <c r="O20" s="24" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="8" t="n">
@@ -2125,13 +2097,10 @@
       </c>
       <c r="J21" s="9" t="n"/>
       <c r="K21" s="10" t="inlineStr"/>
-      <c r="L21" s="11" t="n"/>
-      <c r="M21" s="11" t="n"/>
-      <c r="N21" s="11" t="n"/>
-      <c r="O21" s="11" t="n"/>
-      <c r="P21" s="11" t="n"/>
-      <c r="Q21" s="9" t="n"/>
-      <c r="R21" s="22" t="n"/>
+      <c r="L21" s="9" t="n"/>
+      <c r="M21" s="9" t="n"/>
+      <c r="N21" s="9" t="n"/>
+      <c r="O21" s="22" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="12" t="n">
@@ -2179,13 +2148,10 @@
       </c>
       <c r="J22" s="13" t="n"/>
       <c r="K22" s="14" t="inlineStr"/>
-      <c r="L22" s="15" t="n"/>
-      <c r="M22" s="15" t="n"/>
-      <c r="N22" s="15" t="n"/>
-      <c r="O22" s="15" t="n"/>
-      <c r="P22" s="15" t="n"/>
-      <c r="Q22" s="13" t="n"/>
-      <c r="R22" s="24" t="n"/>
+      <c r="L22" s="13" t="n"/>
+      <c r="M22" s="13" t="n"/>
+      <c r="N22" s="13" t="n"/>
+      <c r="O22" s="24" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="8" t="n">
@@ -2233,13 +2199,10 @@
       </c>
       <c r="J23" s="9" t="n"/>
       <c r="K23" s="10" t="inlineStr"/>
-      <c r="L23" s="11" t="n"/>
-      <c r="M23" s="11" t="n"/>
-      <c r="N23" s="11" t="n"/>
-      <c r="O23" s="11" t="n"/>
-      <c r="P23" s="11" t="n"/>
-      <c r="Q23" s="9" t="n"/>
-      <c r="R23" s="22" t="n"/>
+      <c r="L23" s="9" t="n"/>
+      <c r="M23" s="9" t="n"/>
+      <c r="N23" s="9" t="n"/>
+      <c r="O23" s="22" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="12" t="n">
@@ -2287,13 +2250,10 @@
       </c>
       <c r="J24" s="13" t="n"/>
       <c r="K24" s="14" t="inlineStr"/>
-      <c r="L24" s="15" t="n"/>
-      <c r="M24" s="15" t="n"/>
-      <c r="N24" s="15" t="n"/>
-      <c r="O24" s="15" t="n"/>
-      <c r="P24" s="15" t="n"/>
-      <c r="Q24" s="13" t="n"/>
-      <c r="R24" s="24" t="n"/>
+      <c r="L24" s="13" t="n"/>
+      <c r="M24" s="13" t="n"/>
+      <c r="N24" s="13" t="n"/>
+      <c r="O24" s="24" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="8" t="n">
@@ -2341,13 +2301,10 @@
       </c>
       <c r="J25" s="9" t="n"/>
       <c r="K25" s="10" t="inlineStr"/>
-      <c r="L25" s="11" t="n"/>
-      <c r="M25" s="11" t="n"/>
-      <c r="N25" s="11" t="n"/>
-      <c r="O25" s="11" t="n"/>
-      <c r="P25" s="11" t="n"/>
-      <c r="Q25" s="9" t="n"/>
-      <c r="R25" s="22" t="n"/>
+      <c r="L25" s="9" t="n"/>
+      <c r="M25" s="9" t="n"/>
+      <c r="N25" s="9" t="n"/>
+      <c r="O25" s="22" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="12" t="n">
@@ -2395,13 +2352,10 @@
       </c>
       <c r="J26" s="13" t="n"/>
       <c r="K26" s="14" t="inlineStr"/>
-      <c r="L26" s="15" t="n"/>
-      <c r="M26" s="15" t="n"/>
-      <c r="N26" s="15" t="n"/>
-      <c r="O26" s="15" t="n"/>
-      <c r="P26" s="15" t="n"/>
-      <c r="Q26" s="13" t="n"/>
-      <c r="R26" s="24" t="n"/>
+      <c r="L26" s="13" t="n"/>
+      <c r="M26" s="13" t="n"/>
+      <c r="N26" s="13" t="n"/>
+      <c r="O26" s="24" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="8" t="n">
@@ -2449,13 +2403,10 @@
       </c>
       <c r="J27" s="9" t="n"/>
       <c r="K27" s="10" t="inlineStr"/>
-      <c r="L27" s="11" t="n"/>
-      <c r="M27" s="11" t="n"/>
-      <c r="N27" s="11" t="n"/>
-      <c r="O27" s="11" t="n"/>
-      <c r="P27" s="11" t="n"/>
-      <c r="Q27" s="9" t="n"/>
-      <c r="R27" s="22" t="n"/>
+      <c r="L27" s="9" t="n"/>
+      <c r="M27" s="9" t="n"/>
+      <c r="N27" s="9" t="n"/>
+      <c r="O27" s="22" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="12" t="n">
@@ -2503,13 +2454,10 @@
       </c>
       <c r="J28" s="13" t="n"/>
       <c r="K28" s="14" t="inlineStr"/>
-      <c r="L28" s="15" t="n"/>
-      <c r="M28" s="15" t="n"/>
-      <c r="N28" s="15" t="n"/>
-      <c r="O28" s="15" t="n"/>
-      <c r="P28" s="15" t="n"/>
-      <c r="Q28" s="13" t="n"/>
-      <c r="R28" s="24" t="n"/>
+      <c r="L28" s="13" t="n"/>
+      <c r="M28" s="13" t="n"/>
+      <c r="N28" s="13" t="n"/>
+      <c r="O28" s="24" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="8" t="n">
@@ -2557,13 +2505,10 @@
       </c>
       <c r="J29" s="9" t="n"/>
       <c r="K29" s="10" t="inlineStr"/>
-      <c r="L29" s="11" t="n"/>
-      <c r="M29" s="11" t="n"/>
-      <c r="N29" s="11" t="n"/>
-      <c r="O29" s="11" t="n"/>
-      <c r="P29" s="11" t="n"/>
-      <c r="Q29" s="9" t="n"/>
-      <c r="R29" s="22" t="n"/>
+      <c r="L29" s="9" t="n"/>
+      <c r="M29" s="9" t="n"/>
+      <c r="N29" s="9" t="n"/>
+      <c r="O29" s="22" t="n"/>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="12" t="n">
@@ -2611,13 +2556,10 @@
       </c>
       <c r="J30" s="13" t="n"/>
       <c r="K30" s="14" t="inlineStr"/>
-      <c r="L30" s="15" t="n"/>
-      <c r="M30" s="15" t="n"/>
-      <c r="N30" s="15" t="n"/>
-      <c r="O30" s="15" t="n"/>
-      <c r="P30" s="15" t="n"/>
-      <c r="Q30" s="13" t="n"/>
-      <c r="R30" s="24" t="n"/>
+      <c r="L30" s="13" t="n"/>
+      <c r="M30" s="13" t="n"/>
+      <c r="N30" s="13" t="n"/>
+      <c r="O30" s="24" t="n"/>
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="8" t="n">
@@ -2665,13 +2607,10 @@
       </c>
       <c r="J31" s="9" t="n"/>
       <c r="K31" s="10" t="inlineStr"/>
-      <c r="L31" s="11" t="n"/>
-      <c r="M31" s="11" t="n"/>
-      <c r="N31" s="11" t="n"/>
-      <c r="O31" s="11" t="n"/>
-      <c r="P31" s="11" t="n"/>
-      <c r="Q31" s="9" t="n"/>
-      <c r="R31" s="22" t="n"/>
+      <c r="L31" s="9" t="n"/>
+      <c r="M31" s="9" t="n"/>
+      <c r="N31" s="9" t="n"/>
+      <c r="O31" s="22" t="n"/>
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="12" t="n">
@@ -2719,13 +2658,10 @@
       </c>
       <c r="J32" s="13" t="n"/>
       <c r="K32" s="14" t="inlineStr"/>
-      <c r="L32" s="15" t="n"/>
-      <c r="M32" s="15" t="n"/>
-      <c r="N32" s="15" t="n"/>
-      <c r="O32" s="15" t="n"/>
-      <c r="P32" s="15" t="n"/>
-      <c r="Q32" s="13" t="n"/>
-      <c r="R32" s="24" t="n"/>
+      <c r="L32" s="13" t="n"/>
+      <c r="M32" s="13" t="n"/>
+      <c r="N32" s="13" t="n"/>
+      <c r="O32" s="24" t="n"/>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="8" t="n">
@@ -2773,13 +2709,10 @@
       </c>
       <c r="J33" s="9" t="n"/>
       <c r="K33" s="10" t="inlineStr"/>
-      <c r="L33" s="11" t="n"/>
-      <c r="M33" s="11" t="n"/>
-      <c r="N33" s="11" t="n"/>
-      <c r="O33" s="11" t="n"/>
-      <c r="P33" s="11" t="n"/>
-      <c r="Q33" s="9" t="n"/>
-      <c r="R33" s="22" t="n"/>
+      <c r="L33" s="9" t="n"/>
+      <c r="M33" s="9" t="n"/>
+      <c r="N33" s="9" t="n"/>
+      <c r="O33" s="22" t="n"/>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="12" t="n">
@@ -2827,13 +2760,10 @@
       </c>
       <c r="J34" s="13" t="n"/>
       <c r="K34" s="14" t="inlineStr"/>
-      <c r="L34" s="15" t="n"/>
-      <c r="M34" s="15" t="n"/>
-      <c r="N34" s="15" t="n"/>
-      <c r="O34" s="15" t="n"/>
-      <c r="P34" s="15" t="n"/>
-      <c r="Q34" s="13" t="n"/>
-      <c r="R34" s="24" t="n"/>
+      <c r="L34" s="13" t="n"/>
+      <c r="M34" s="13" t="n"/>
+      <c r="N34" s="13" t="n"/>
+      <c r="O34" s="24" t="n"/>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="8" t="n">
@@ -2881,13 +2811,10 @@
       </c>
       <c r="J35" s="9" t="n"/>
       <c r="K35" s="10" t="inlineStr"/>
-      <c r="L35" s="11" t="n"/>
-      <c r="M35" s="11" t="n"/>
-      <c r="N35" s="11" t="n"/>
-      <c r="O35" s="11" t="n"/>
-      <c r="P35" s="11" t="n"/>
-      <c r="Q35" s="9" t="n"/>
-      <c r="R35" s="22" t="n"/>
+      <c r="L35" s="9" t="n"/>
+      <c r="M35" s="9" t="n"/>
+      <c r="N35" s="9" t="n"/>
+      <c r="O35" s="22" t="n"/>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="12" t="n">
@@ -2935,13 +2862,10 @@
       </c>
       <c r="J36" s="13" t="n"/>
       <c r="K36" s="14" t="inlineStr"/>
-      <c r="L36" s="15" t="n"/>
-      <c r="M36" s="15" t="n"/>
-      <c r="N36" s="15" t="n"/>
-      <c r="O36" s="15" t="n"/>
-      <c r="P36" s="15" t="n"/>
-      <c r="Q36" s="13" t="n"/>
-      <c r="R36" s="24" t="n"/>
+      <c r="L36" s="13" t="n"/>
+      <c r="M36" s="13" t="n"/>
+      <c r="N36" s="13" t="n"/>
+      <c r="O36" s="24" t="n"/>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="8" t="n">
@@ -2989,13 +2913,10 @@
       </c>
       <c r="J37" s="9" t="n"/>
       <c r="K37" s="10" t="inlineStr"/>
-      <c r="L37" s="11" t="n"/>
-      <c r="M37" s="11" t="n"/>
-      <c r="N37" s="11" t="n"/>
-      <c r="O37" s="11" t="n"/>
-      <c r="P37" s="11" t="n"/>
-      <c r="Q37" s="9" t="n"/>
-      <c r="R37" s="22" t="n"/>
+      <c r="L37" s="9" t="n"/>
+      <c r="M37" s="9" t="n"/>
+      <c r="N37" s="9" t="n"/>
+      <c r="O37" s="22" t="n"/>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="12" t="n">
@@ -3043,13 +2964,10 @@
       </c>
       <c r="J38" s="13" t="n"/>
       <c r="K38" s="14" t="inlineStr"/>
-      <c r="L38" s="15" t="n"/>
-      <c r="M38" s="15" t="n"/>
-      <c r="N38" s="15" t="n"/>
-      <c r="O38" s="15" t="n"/>
-      <c r="P38" s="15" t="n"/>
-      <c r="Q38" s="13" t="n"/>
-      <c r="R38" s="24" t="n"/>
+      <c r="L38" s="13" t="n"/>
+      <c r="M38" s="13" t="n"/>
+      <c r="N38" s="13" t="n"/>
+      <c r="O38" s="24" t="n"/>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="8" t="n">
@@ -3097,13 +3015,10 @@
       </c>
       <c r="J39" s="9" t="n"/>
       <c r="K39" s="10" t="inlineStr"/>
-      <c r="L39" s="11" t="n"/>
-      <c r="M39" s="11" t="n"/>
-      <c r="N39" s="11" t="n"/>
-      <c r="O39" s="11" t="n"/>
-      <c r="P39" s="11" t="n"/>
-      <c r="Q39" s="9" t="n"/>
-      <c r="R39" s="22" t="n"/>
+      <c r="L39" s="9" t="n"/>
+      <c r="M39" s="9" t="n"/>
+      <c r="N39" s="9" t="n"/>
+      <c r="O39" s="22" t="n"/>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="12" t="n">
@@ -3151,13 +3066,10 @@
       </c>
       <c r="J40" s="13" t="n"/>
       <c r="K40" s="14" t="inlineStr"/>
-      <c r="L40" s="15" t="n"/>
-      <c r="M40" s="15" t="n"/>
-      <c r="N40" s="15" t="n"/>
-      <c r="O40" s="15" t="n"/>
-      <c r="P40" s="15" t="n"/>
-      <c r="Q40" s="13" t="n"/>
-      <c r="R40" s="24" t="n"/>
+      <c r="L40" s="13" t="n"/>
+      <c r="M40" s="13" t="n"/>
+      <c r="N40" s="13" t="n"/>
+      <c r="O40" s="24" t="n"/>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="8" t="n">
@@ -3205,13 +3117,10 @@
       </c>
       <c r="J41" s="9" t="n"/>
       <c r="K41" s="10" t="inlineStr"/>
-      <c r="L41" s="11" t="n"/>
-      <c r="M41" s="11" t="n"/>
-      <c r="N41" s="11" t="n"/>
-      <c r="O41" s="11" t="n"/>
-      <c r="P41" s="11" t="n"/>
-      <c r="Q41" s="9" t="n"/>
-      <c r="R41" s="22" t="n"/>
+      <c r="L41" s="9" t="n"/>
+      <c r="M41" s="9" t="n"/>
+      <c r="N41" s="9" t="n"/>
+      <c r="O41" s="22" t="n"/>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="12" t="n">
@@ -3259,13 +3168,10 @@
       </c>
       <c r="J42" s="13" t="n"/>
       <c r="K42" s="14" t="inlineStr"/>
-      <c r="L42" s="15" t="n"/>
-      <c r="M42" s="15" t="n"/>
-      <c r="N42" s="15" t="n"/>
-      <c r="O42" s="15" t="n"/>
-      <c r="P42" s="15" t="n"/>
-      <c r="Q42" s="13" t="n"/>
-      <c r="R42" s="24" t="n"/>
+      <c r="L42" s="13" t="n"/>
+      <c r="M42" s="13" t="n"/>
+      <c r="N42" s="13" t="n"/>
+      <c r="O42" s="24" t="n"/>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="8" t="n">
@@ -3313,13 +3219,10 @@
       </c>
       <c r="J43" s="9" t="n"/>
       <c r="K43" s="10" t="inlineStr"/>
-      <c r="L43" s="11" t="n"/>
-      <c r="M43" s="11" t="n"/>
-      <c r="N43" s="11" t="n"/>
-      <c r="O43" s="11" t="n"/>
-      <c r="P43" s="11" t="n"/>
-      <c r="Q43" s="9" t="n"/>
-      <c r="R43" s="22" t="n"/>
+      <c r="L43" s="9" t="n"/>
+      <c r="M43" s="9" t="n"/>
+      <c r="N43" s="9" t="n"/>
+      <c r="O43" s="22" t="n"/>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="12" t="n">
@@ -3367,13 +3270,10 @@
       </c>
       <c r="J44" s="13" t="n"/>
       <c r="K44" s="14" t="inlineStr"/>
-      <c r="L44" s="15" t="n"/>
-      <c r="M44" s="15" t="n"/>
-      <c r="N44" s="15" t="n"/>
-      <c r="O44" s="15" t="n"/>
-      <c r="P44" s="15" t="n"/>
-      <c r="Q44" s="13" t="n"/>
-      <c r="R44" s="24" t="n"/>
+      <c r="L44" s="13" t="n"/>
+      <c r="M44" s="13" t="n"/>
+      <c r="N44" s="13" t="n"/>
+      <c r="O44" s="24" t="n"/>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="8" t="n">
@@ -3421,13 +3321,10 @@
       </c>
       <c r="J45" s="9" t="n"/>
       <c r="K45" s="10" t="inlineStr"/>
-      <c r="L45" s="11" t="n"/>
-      <c r="M45" s="11" t="n"/>
-      <c r="N45" s="11" t="n"/>
-      <c r="O45" s="11" t="n"/>
-      <c r="P45" s="11" t="n"/>
-      <c r="Q45" s="9" t="n"/>
-      <c r="R45" s="22" t="n"/>
+      <c r="L45" s="9" t="n"/>
+      <c r="M45" s="9" t="n"/>
+      <c r="N45" s="9" t="n"/>
+      <c r="O45" s="22" t="n"/>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="12" t="n">
@@ -3475,13 +3372,10 @@
       </c>
       <c r="J46" s="13" t="n"/>
       <c r="K46" s="14" t="inlineStr"/>
-      <c r="L46" s="15" t="n"/>
-      <c r="M46" s="15" t="n"/>
-      <c r="N46" s="15" t="n"/>
-      <c r="O46" s="15" t="n"/>
-      <c r="P46" s="15" t="n"/>
-      <c r="Q46" s="13" t="n"/>
-      <c r="R46" s="24" t="n"/>
+      <c r="L46" s="13" t="n"/>
+      <c r="M46" s="13" t="n"/>
+      <c r="N46" s="13" t="n"/>
+      <c r="O46" s="24" t="n"/>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="8" t="n">
@@ -3529,13 +3423,10 @@
       </c>
       <c r="J47" s="9" t="n"/>
       <c r="K47" s="10" t="inlineStr"/>
-      <c r="L47" s="11" t="n"/>
-      <c r="M47" s="11" t="n"/>
-      <c r="N47" s="11" t="n"/>
-      <c r="O47" s="11" t="n"/>
-      <c r="P47" s="11" t="n"/>
-      <c r="Q47" s="9" t="n"/>
-      <c r="R47" s="22" t="n"/>
+      <c r="L47" s="9" t="n"/>
+      <c r="M47" s="9" t="n"/>
+      <c r="N47" s="9" t="n"/>
+      <c r="O47" s="22" t="n"/>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="12" t="n">
@@ -3583,13 +3474,10 @@
       </c>
       <c r="J48" s="13" t="n"/>
       <c r="K48" s="14" t="inlineStr"/>
-      <c r="L48" s="15" t="n"/>
-      <c r="M48" s="15" t="n"/>
-      <c r="N48" s="15" t="n"/>
-      <c r="O48" s="15" t="n"/>
-      <c r="P48" s="15" t="n"/>
-      <c r="Q48" s="13" t="n"/>
-      <c r="R48" s="24" t="n"/>
+      <c r="L48" s="13" t="n"/>
+      <c r="M48" s="13" t="n"/>
+      <c r="N48" s="13" t="n"/>
+      <c r="O48" s="24" t="n"/>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="8" t="n">
@@ -3637,13 +3525,10 @@
       </c>
       <c r="J49" s="9" t="n"/>
       <c r="K49" s="10" t="inlineStr"/>
-      <c r="L49" s="11" t="n"/>
-      <c r="M49" s="11" t="n"/>
-      <c r="N49" s="11" t="n"/>
-      <c r="O49" s="11" t="n"/>
-      <c r="P49" s="11" t="n"/>
-      <c r="Q49" s="9" t="n"/>
-      <c r="R49" s="22" t="n"/>
+      <c r="L49" s="9" t="n"/>
+      <c r="M49" s="9" t="n"/>
+      <c r="N49" s="9" t="n"/>
+      <c r="O49" s="22" t="n"/>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="12" t="n">
@@ -3691,13 +3576,10 @@
       </c>
       <c r="J50" s="13" t="n"/>
       <c r="K50" s="14" t="inlineStr"/>
-      <c r="L50" s="15" t="n"/>
-      <c r="M50" s="15" t="n"/>
-      <c r="N50" s="15" t="n"/>
-      <c r="O50" s="15" t="n"/>
-      <c r="P50" s="15" t="n"/>
-      <c r="Q50" s="13" t="n"/>
-      <c r="R50" s="24" t="n"/>
+      <c r="L50" s="13" t="n"/>
+      <c r="M50" s="13" t="n"/>
+      <c r="N50" s="13" t="n"/>
+      <c r="O50" s="24" t="n"/>
     </row>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="8" t="n">
@@ -3745,13 +3627,10 @@
       </c>
       <c r="J51" s="9" t="n"/>
       <c r="K51" s="10" t="inlineStr"/>
-      <c r="L51" s="11" t="n"/>
-      <c r="M51" s="11" t="n"/>
-      <c r="N51" s="11" t="n"/>
-      <c r="O51" s="11" t="n"/>
-      <c r="P51" s="11" t="n"/>
-      <c r="Q51" s="9" t="n"/>
-      <c r="R51" s="22" t="n"/>
+      <c r="L51" s="9" t="n"/>
+      <c r="M51" s="9" t="n"/>
+      <c r="N51" s="9" t="n"/>
+      <c r="O51" s="22" t="n"/>
     </row>
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="12" t="n">
@@ -3799,13 +3678,10 @@
       </c>
       <c r="J52" s="13" t="n"/>
       <c r="K52" s="14" t="inlineStr"/>
-      <c r="L52" s="15" t="n"/>
-      <c r="M52" s="15" t="n"/>
-      <c r="N52" s="15" t="n"/>
-      <c r="O52" s="15" t="n"/>
-      <c r="P52" s="15" t="n"/>
-      <c r="Q52" s="13" t="n"/>
-      <c r="R52" s="24" t="n"/>
+      <c r="L52" s="13" t="n"/>
+      <c r="M52" s="13" t="n"/>
+      <c r="N52" s="13" t="n"/>
+      <c r="O52" s="24" t="n"/>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="8" t="n">
@@ -3853,13 +3729,10 @@
       </c>
       <c r="J53" s="9" t="n"/>
       <c r="K53" s="10" t="inlineStr"/>
-      <c r="L53" s="11" t="n"/>
-      <c r="M53" s="11" t="n"/>
-      <c r="N53" s="11" t="n"/>
-      <c r="O53" s="11" t="n"/>
-      <c r="P53" s="11" t="n"/>
-      <c r="Q53" s="9" t="n"/>
-      <c r="R53" s="22" t="n"/>
+      <c r="L53" s="9" t="n"/>
+      <c r="M53" s="9" t="n"/>
+      <c r="N53" s="9" t="n"/>
+      <c r="O53" s="22" t="n"/>
     </row>
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="12" t="n">
@@ -3907,13 +3780,10 @@
       </c>
       <c r="J54" s="13" t="n"/>
       <c r="K54" s="14" t="inlineStr"/>
-      <c r="L54" s="15" t="n"/>
-      <c r="M54" s="15" t="n"/>
-      <c r="N54" s="15" t="n"/>
-      <c r="O54" s="15" t="n"/>
-      <c r="P54" s="15" t="n"/>
-      <c r="Q54" s="13" t="n"/>
-      <c r="R54" s="24" t="n"/>
+      <c r="L54" s="13" t="n"/>
+      <c r="M54" s="13" t="n"/>
+      <c r="N54" s="13" t="n"/>
+      <c r="O54" s="24" t="n"/>
     </row>
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="8" t="n">
@@ -3961,13 +3831,10 @@
       </c>
       <c r="J55" s="9" t="n"/>
       <c r="K55" s="10" t="inlineStr"/>
-      <c r="L55" s="11" t="n"/>
-      <c r="M55" s="11" t="n"/>
-      <c r="N55" s="11" t="n"/>
-      <c r="O55" s="11" t="n"/>
-      <c r="P55" s="11" t="n"/>
-      <c r="Q55" s="9" t="n"/>
-      <c r="R55" s="22" t="n"/>
+      <c r="L55" s="9" t="n"/>
+      <c r="M55" s="9" t="n"/>
+      <c r="N55" s="9" t="n"/>
+      <c r="O55" s="22" t="n"/>
     </row>
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="12" t="n">
@@ -4015,13 +3882,10 @@
       </c>
       <c r="J56" s="13" t="n"/>
       <c r="K56" s="14" t="inlineStr"/>
-      <c r="L56" s="15" t="n"/>
-      <c r="M56" s="15" t="n"/>
-      <c r="N56" s="15" t="n"/>
-      <c r="O56" s="15" t="n"/>
-      <c r="P56" s="15" t="n"/>
-      <c r="Q56" s="13" t="n"/>
-      <c r="R56" s="24" t="n"/>
+      <c r="L56" s="13" t="n"/>
+      <c r="M56" s="13" t="n"/>
+      <c r="N56" s="13" t="n"/>
+      <c r="O56" s="24" t="n"/>
     </row>
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="8" t="n">
@@ -4069,13 +3933,10 @@
       </c>
       <c r="J57" s="9" t="n"/>
       <c r="K57" s="10" t="inlineStr"/>
-      <c r="L57" s="11" t="n"/>
-      <c r="M57" s="11" t="n"/>
-      <c r="N57" s="11" t="n"/>
-      <c r="O57" s="11" t="n"/>
-      <c r="P57" s="11" t="n"/>
-      <c r="Q57" s="9" t="n"/>
-      <c r="R57" s="22" t="n"/>
+      <c r="L57" s="9" t="n"/>
+      <c r="M57" s="9" t="n"/>
+      <c r="N57" s="9" t="n"/>
+      <c r="O57" s="22" t="n"/>
     </row>
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="12" t="n">
@@ -4123,13 +3984,10 @@
       </c>
       <c r="J58" s="13" t="n"/>
       <c r="K58" s="14" t="inlineStr"/>
-      <c r="L58" s="15" t="n"/>
-      <c r="M58" s="15" t="n"/>
-      <c r="N58" s="15" t="n"/>
-      <c r="O58" s="15" t="n"/>
-      <c r="P58" s="15" t="n"/>
-      <c r="Q58" s="13" t="n"/>
-      <c r="R58" s="24" t="n"/>
+      <c r="L58" s="13" t="n"/>
+      <c r="M58" s="13" t="n"/>
+      <c r="N58" s="13" t="n"/>
+      <c r="O58" s="24" t="n"/>
     </row>
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="8" t="n">
@@ -4177,13 +4035,10 @@
       </c>
       <c r="J59" s="9" t="n"/>
       <c r="K59" s="10" t="inlineStr"/>
-      <c r="L59" s="11" t="n"/>
-      <c r="M59" s="11" t="n"/>
-      <c r="N59" s="11" t="n"/>
-      <c r="O59" s="11" t="n"/>
-      <c r="P59" s="11" t="n"/>
-      <c r="Q59" s="9" t="n"/>
-      <c r="R59" s="22" t="n"/>
+      <c r="L59" s="9" t="n"/>
+      <c r="M59" s="9" t="n"/>
+      <c r="N59" s="9" t="n"/>
+      <c r="O59" s="22" t="n"/>
     </row>
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="12" t="n">
@@ -4231,13 +4086,10 @@
       </c>
       <c r="J60" s="13" t="n"/>
       <c r="K60" s="14" t="inlineStr"/>
-      <c r="L60" s="15" t="n"/>
-      <c r="M60" s="15" t="n"/>
-      <c r="N60" s="15" t="n"/>
-      <c r="O60" s="15" t="n"/>
-      <c r="P60" s="15" t="n"/>
-      <c r="Q60" s="13" t="n"/>
-      <c r="R60" s="24" t="n"/>
+      <c r="L60" s="13" t="n"/>
+      <c r="M60" s="13" t="n"/>
+      <c r="N60" s="13" t="n"/>
+      <c r="O60" s="24" t="n"/>
     </row>
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="8" t="n">
@@ -4285,13 +4137,10 @@
       </c>
       <c r="J61" s="9" t="n"/>
       <c r="K61" s="10" t="inlineStr"/>
-      <c r="L61" s="11" t="n"/>
-      <c r="M61" s="11" t="n"/>
-      <c r="N61" s="11" t="n"/>
-      <c r="O61" s="11" t="n"/>
-      <c r="P61" s="11" t="n"/>
-      <c r="Q61" s="9" t="n"/>
-      <c r="R61" s="22" t="n"/>
+      <c r="L61" s="9" t="n"/>
+      <c r="M61" s="9" t="n"/>
+      <c r="N61" s="9" t="n"/>
+      <c r="O61" s="22" t="n"/>
     </row>
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="12" t="n">
@@ -4339,13 +4188,10 @@
       </c>
       <c r="J62" s="13" t="n"/>
       <c r="K62" s="14" t="inlineStr"/>
-      <c r="L62" s="15" t="n"/>
-      <c r="M62" s="15" t="n"/>
-      <c r="N62" s="15" t="n"/>
-      <c r="O62" s="15" t="n"/>
-      <c r="P62" s="15" t="n"/>
-      <c r="Q62" s="13" t="n"/>
-      <c r="R62" s="24" t="n"/>
+      <c r="L62" s="13" t="n"/>
+      <c r="M62" s="13" t="n"/>
+      <c r="N62" s="13" t="n"/>
+      <c r="O62" s="24" t="n"/>
     </row>
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="8" t="n">
@@ -4393,13 +4239,10 @@
       </c>
       <c r="J63" s="9" t="n"/>
       <c r="K63" s="10" t="inlineStr"/>
-      <c r="L63" s="11" t="n"/>
-      <c r="M63" s="11" t="n"/>
-      <c r="N63" s="11" t="n"/>
-      <c r="O63" s="11" t="n"/>
-      <c r="P63" s="11" t="n"/>
-      <c r="Q63" s="9" t="n"/>
-      <c r="R63" s="22" t="n"/>
+      <c r="L63" s="9" t="n"/>
+      <c r="M63" s="9" t="n"/>
+      <c r="N63" s="9" t="n"/>
+      <c r="O63" s="22" t="n"/>
     </row>
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="12" t="n">
@@ -4447,13 +4290,10 @@
       </c>
       <c r="J64" s="13" t="n"/>
       <c r="K64" s="14" t="inlineStr"/>
-      <c r="L64" s="15" t="n"/>
-      <c r="M64" s="15" t="n"/>
-      <c r="N64" s="15" t="n"/>
-      <c r="O64" s="15" t="n"/>
-      <c r="P64" s="15" t="n"/>
-      <c r="Q64" s="13" t="n"/>
-      <c r="R64" s="24" t="n"/>
+      <c r="L64" s="13" t="n"/>
+      <c r="M64" s="13" t="n"/>
+      <c r="N64" s="13" t="n"/>
+      <c r="O64" s="24" t="n"/>
     </row>
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="8" t="n">
@@ -4501,13 +4341,10 @@
       </c>
       <c r="J65" s="9" t="n"/>
       <c r="K65" s="10" t="inlineStr"/>
-      <c r="L65" s="11" t="n"/>
-      <c r="M65" s="11" t="n"/>
-      <c r="N65" s="11" t="n"/>
-      <c r="O65" s="11" t="n"/>
-      <c r="P65" s="11" t="n"/>
-      <c r="Q65" s="9" t="n"/>
-      <c r="R65" s="22" t="n"/>
+      <c r="L65" s="9" t="n"/>
+      <c r="M65" s="9" t="n"/>
+      <c r="N65" s="9" t="n"/>
+      <c r="O65" s="22" t="n"/>
     </row>
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="12" t="n">
@@ -4555,13 +4392,10 @@
       </c>
       <c r="J66" s="13" t="n"/>
       <c r="K66" s="14" t="inlineStr"/>
-      <c r="L66" s="15" t="n"/>
-      <c r="M66" s="15" t="n"/>
-      <c r="N66" s="15" t="n"/>
-      <c r="O66" s="15" t="n"/>
-      <c r="P66" s="15" t="n"/>
-      <c r="Q66" s="13" t="n"/>
-      <c r="R66" s="24" t="n"/>
+      <c r="L66" s="13" t="n"/>
+      <c r="M66" s="13" t="n"/>
+      <c r="N66" s="13" t="n"/>
+      <c r="O66" s="24" t="n"/>
     </row>
     <row r="67" ht="22" customHeight="1">
       <c r="A67" s="8" t="n">
@@ -4609,13 +4443,10 @@
       </c>
       <c r="J67" s="9" t="n"/>
       <c r="K67" s="10" t="inlineStr"/>
-      <c r="L67" s="11" t="n"/>
-      <c r="M67" s="11" t="n"/>
-      <c r="N67" s="11" t="n"/>
-      <c r="O67" s="11" t="n"/>
-      <c r="P67" s="11" t="n"/>
-      <c r="Q67" s="9" t="n"/>
-      <c r="R67" s="22" t="n"/>
+      <c r="L67" s="9" t="n"/>
+      <c r="M67" s="9" t="n"/>
+      <c r="N67" s="9" t="n"/>
+      <c r="O67" s="22" t="n"/>
     </row>
     <row r="68" ht="22" customHeight="1">
       <c r="A68" s="12" t="n">
@@ -4663,13 +4494,10 @@
       </c>
       <c r="J68" s="13" t="n"/>
       <c r="K68" s="14" t="inlineStr"/>
-      <c r="L68" s="15" t="n"/>
-      <c r="M68" s="15" t="n"/>
-      <c r="N68" s="15" t="n"/>
-      <c r="O68" s="15" t="n"/>
-      <c r="P68" s="15" t="n"/>
-      <c r="Q68" s="13" t="n"/>
-      <c r="R68" s="24" t="n"/>
+      <c r="L68" s="13" t="n"/>
+      <c r="M68" s="13" t="n"/>
+      <c r="N68" s="13" t="n"/>
+      <c r="O68" s="24" t="n"/>
     </row>
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="8" t="n">
@@ -4717,13 +4545,10 @@
       </c>
       <c r="J69" s="9" t="n"/>
       <c r="K69" s="10" t="inlineStr"/>
-      <c r="L69" s="11" t="n"/>
-      <c r="M69" s="11" t="n"/>
-      <c r="N69" s="11" t="n"/>
-      <c r="O69" s="11" t="n"/>
-      <c r="P69" s="11" t="n"/>
-      <c r="Q69" s="9" t="n"/>
-      <c r="R69" s="22" t="n"/>
+      <c r="L69" s="9" t="n"/>
+      <c r="M69" s="9" t="n"/>
+      <c r="N69" s="9" t="n"/>
+      <c r="O69" s="22" t="n"/>
     </row>
     <row r="70" ht="22" customHeight="1">
       <c r="A70" s="12" t="n">
@@ -4771,13 +4596,10 @@
       </c>
       <c r="J70" s="13" t="n"/>
       <c r="K70" s="14" t="inlineStr"/>
-      <c r="L70" s="15" t="n"/>
-      <c r="M70" s="15" t="n"/>
-      <c r="N70" s="15" t="n"/>
-      <c r="O70" s="15" t="n"/>
-      <c r="P70" s="15" t="n"/>
-      <c r="Q70" s="13" t="n"/>
-      <c r="R70" s="24" t="n"/>
+      <c r="L70" s="13" t="n"/>
+      <c r="M70" s="13" t="n"/>
+      <c r="N70" s="13" t="n"/>
+      <c r="O70" s="24" t="n"/>
     </row>
     <row r="71" ht="22" customHeight="1">
       <c r="A71" s="8" t="n">
@@ -4825,13 +4647,10 @@
       </c>
       <c r="J71" s="9" t="n"/>
       <c r="K71" s="10" t="inlineStr"/>
-      <c r="L71" s="11" t="n"/>
-      <c r="M71" s="11" t="n"/>
-      <c r="N71" s="11" t="n"/>
-      <c r="O71" s="11" t="n"/>
-      <c r="P71" s="11" t="n"/>
-      <c r="Q71" s="9" t="n"/>
-      <c r="R71" s="22" t="n"/>
+      <c r="L71" s="9" t="n"/>
+      <c r="M71" s="9" t="n"/>
+      <c r="N71" s="9" t="n"/>
+      <c r="O71" s="22" t="n"/>
     </row>
     <row r="72" ht="22" customHeight="1">
       <c r="A72" s="12" t="n">
@@ -4879,13 +4698,10 @@
       </c>
       <c r="J72" s="13" t="n"/>
       <c r="K72" s="14" t="inlineStr"/>
-      <c r="L72" s="15" t="n"/>
-      <c r="M72" s="15" t="n"/>
-      <c r="N72" s="15" t="n"/>
-      <c r="O72" s="15" t="n"/>
-      <c r="P72" s="15" t="n"/>
-      <c r="Q72" s="13" t="n"/>
-      <c r="R72" s="24" t="n"/>
+      <c r="L72" s="13" t="n"/>
+      <c r="M72" s="13" t="n"/>
+      <c r="N72" s="13" t="n"/>
+      <c r="O72" s="24" t="n"/>
     </row>
     <row r="73" ht="22" customHeight="1">
       <c r="A73" s="8" t="n">
@@ -4933,13 +4749,10 @@
       </c>
       <c r="J73" s="9" t="n"/>
       <c r="K73" s="10" t="inlineStr"/>
-      <c r="L73" s="11" t="n"/>
-      <c r="M73" s="11" t="n"/>
-      <c r="N73" s="11" t="n"/>
-      <c r="O73" s="11" t="n"/>
-      <c r="P73" s="11" t="n"/>
-      <c r="Q73" s="9" t="n"/>
-      <c r="R73" s="22" t="n"/>
+      <c r="L73" s="9" t="n"/>
+      <c r="M73" s="9" t="n"/>
+      <c r="N73" s="9" t="n"/>
+      <c r="O73" s="22" t="n"/>
     </row>
     <row r="74" ht="22" customHeight="1">
       <c r="A74" s="12" t="n">
@@ -4987,13 +4800,10 @@
       </c>
       <c r="J74" s="13" t="n"/>
       <c r="K74" s="14" t="inlineStr"/>
-      <c r="L74" s="15" t="n"/>
-      <c r="M74" s="15" t="n"/>
-      <c r="N74" s="15" t="n"/>
-      <c r="O74" s="15" t="n"/>
-      <c r="P74" s="15" t="n"/>
-      <c r="Q74" s="13" t="n"/>
-      <c r="R74" s="24" t="n"/>
+      <c r="L74" s="13" t="n"/>
+      <c r="M74" s="13" t="n"/>
+      <c r="N74" s="13" t="n"/>
+      <c r="O74" s="24" t="n"/>
     </row>
     <row r="75" ht="22" customHeight="1">
       <c r="A75" s="8" t="n">
@@ -5041,13 +4851,10 @@
       </c>
       <c r="J75" s="9" t="n"/>
       <c r="K75" s="10" t="inlineStr"/>
-      <c r="L75" s="11" t="n"/>
-      <c r="M75" s="11" t="n"/>
-      <c r="N75" s="11" t="n"/>
-      <c r="O75" s="11" t="n"/>
-      <c r="P75" s="11" t="n"/>
-      <c r="Q75" s="9" t="n"/>
-      <c r="R75" s="22" t="n"/>
+      <c r="L75" s="9" t="n"/>
+      <c r="M75" s="9" t="n"/>
+      <c r="N75" s="9" t="n"/>
+      <c r="O75" s="22" t="n"/>
     </row>
     <row r="76" ht="22" customHeight="1">
       <c r="A76" s="12" t="n">
@@ -5095,13 +4902,10 @@
       </c>
       <c r="J76" s="13" t="n"/>
       <c r="K76" s="14" t="inlineStr"/>
-      <c r="L76" s="15" t="n"/>
-      <c r="M76" s="15" t="n"/>
-      <c r="N76" s="15" t="n"/>
-      <c r="O76" s="15" t="n"/>
-      <c r="P76" s="15" t="n"/>
-      <c r="Q76" s="13" t="n"/>
-      <c r="R76" s="24" t="n"/>
+      <c r="L76" s="13" t="n"/>
+      <c r="M76" s="13" t="n"/>
+      <c r="N76" s="13" t="n"/>
+      <c r="O76" s="24" t="n"/>
     </row>
     <row r="77" ht="22" customHeight="1">
       <c r="A77" s="8" t="n">
@@ -5149,13 +4953,10 @@
       </c>
       <c r="J77" s="9" t="n"/>
       <c r="K77" s="10" t="inlineStr"/>
-      <c r="L77" s="11" t="n"/>
-      <c r="M77" s="11" t="n"/>
-      <c r="N77" s="11" t="n"/>
-      <c r="O77" s="11" t="n"/>
-      <c r="P77" s="11" t="n"/>
-      <c r="Q77" s="9" t="n"/>
-      <c r="R77" s="22" t="n"/>
+      <c r="L77" s="9" t="n"/>
+      <c r="M77" s="9" t="n"/>
+      <c r="N77" s="9" t="n"/>
+      <c r="O77" s="22" t="n"/>
     </row>
     <row r="78" ht="22" customHeight="1">
       <c r="A78" s="12" t="n">
@@ -5203,13 +5004,10 @@
       </c>
       <c r="J78" s="13" t="n"/>
       <c r="K78" s="14" t="inlineStr"/>
-      <c r="L78" s="15" t="n"/>
-      <c r="M78" s="15" t="n"/>
-      <c r="N78" s="15" t="n"/>
-      <c r="O78" s="15" t="n"/>
-      <c r="P78" s="15" t="n"/>
-      <c r="Q78" s="13" t="n"/>
-      <c r="R78" s="24" t="n"/>
+      <c r="L78" s="13" t="n"/>
+      <c r="M78" s="13" t="n"/>
+      <c r="N78" s="13" t="n"/>
+      <c r="O78" s="24" t="n"/>
     </row>
     <row r="79" ht="22" customHeight="1">
       <c r="A79" s="8" t="n">
@@ -5257,13 +5055,10 @@
       </c>
       <c r="J79" s="9" t="n"/>
       <c r="K79" s="10" t="inlineStr"/>
-      <c r="L79" s="11" t="n"/>
-      <c r="M79" s="11" t="n"/>
-      <c r="N79" s="11" t="n"/>
-      <c r="O79" s="11" t="n"/>
-      <c r="P79" s="11" t="n"/>
-      <c r="Q79" s="9" t="n"/>
-      <c r="R79" s="22" t="n"/>
+      <c r="L79" s="9" t="n"/>
+      <c r="M79" s="9" t="n"/>
+      <c r="N79" s="9" t="n"/>
+      <c r="O79" s="22" t="n"/>
     </row>
     <row r="80" ht="22" customHeight="1">
       <c r="A80" s="12" t="n">
@@ -5311,13 +5106,10 @@
       </c>
       <c r="J80" s="13" t="n"/>
       <c r="K80" s="14" t="inlineStr"/>
-      <c r="L80" s="15" t="n"/>
-      <c r="M80" s="15" t="n"/>
-      <c r="N80" s="15" t="n"/>
-      <c r="O80" s="15" t="n"/>
-      <c r="P80" s="15" t="n"/>
-      <c r="Q80" s="13" t="n"/>
-      <c r="R80" s="24" t="n"/>
+      <c r="L80" s="13" t="n"/>
+      <c r="M80" s="13" t="n"/>
+      <c r="N80" s="13" t="n"/>
+      <c r="O80" s="24" t="n"/>
     </row>
     <row r="81" ht="22" customHeight="1">
       <c r="A81" s="8" t="n">
@@ -5365,13 +5157,10 @@
       </c>
       <c r="J81" s="9" t="n"/>
       <c r="K81" s="10" t="inlineStr"/>
-      <c r="L81" s="11" t="n"/>
-      <c r="M81" s="11" t="n"/>
-      <c r="N81" s="11" t="n"/>
-      <c r="O81" s="11" t="n"/>
-      <c r="P81" s="11" t="n"/>
-      <c r="Q81" s="9" t="n"/>
-      <c r="R81" s="22" t="n"/>
+      <c r="L81" s="9" t="n"/>
+      <c r="M81" s="9" t="n"/>
+      <c r="N81" s="9" t="n"/>
+      <c r="O81" s="22" t="n"/>
     </row>
     <row r="82" ht="22" customHeight="1">
       <c r="A82" s="12" t="n">
@@ -5419,13 +5208,10 @@
       </c>
       <c r="J82" s="13" t="n"/>
       <c r="K82" s="14" t="inlineStr"/>
-      <c r="L82" s="15" t="n"/>
-      <c r="M82" s="15" t="n"/>
-      <c r="N82" s="15" t="n"/>
-      <c r="O82" s="15" t="n"/>
-      <c r="P82" s="15" t="n"/>
-      <c r="Q82" s="13" t="n"/>
-      <c r="R82" s="24" t="n"/>
+      <c r="L82" s="13" t="n"/>
+      <c r="M82" s="13" t="n"/>
+      <c r="N82" s="13" t="n"/>
+      <c r="O82" s="24" t="n"/>
     </row>
     <row r="83" ht="22" customHeight="1">
       <c r="A83" s="8" t="n">
@@ -5473,13 +5259,10 @@
       </c>
       <c r="J83" s="9" t="n"/>
       <c r="K83" s="10" t="inlineStr"/>
-      <c r="L83" s="11" t="n"/>
-      <c r="M83" s="11" t="n"/>
-      <c r="N83" s="11" t="n"/>
-      <c r="O83" s="11" t="n"/>
-      <c r="P83" s="11" t="n"/>
-      <c r="Q83" s="9" t="n"/>
-      <c r="R83" s="22" t="n"/>
+      <c r="L83" s="9" t="n"/>
+      <c r="M83" s="9" t="n"/>
+      <c r="N83" s="9" t="n"/>
+      <c r="O83" s="22" t="n"/>
     </row>
     <row r="84" ht="22" customHeight="1">
       <c r="A84" s="12" t="n">
@@ -5527,13 +5310,10 @@
       </c>
       <c r="J84" s="13" t="n"/>
       <c r="K84" s="14" t="inlineStr"/>
-      <c r="L84" s="15" t="n"/>
-      <c r="M84" s="15" t="n"/>
-      <c r="N84" s="15" t="n"/>
-      <c r="O84" s="15" t="n"/>
-      <c r="P84" s="15" t="n"/>
-      <c r="Q84" s="13" t="n"/>
-      <c r="R84" s="24" t="n"/>
+      <c r="L84" s="13" t="n"/>
+      <c r="M84" s="13" t="n"/>
+      <c r="N84" s="13" t="n"/>
+      <c r="O84" s="24" t="n"/>
     </row>
     <row r="85" ht="22" customHeight="1">
       <c r="A85" s="8" t="n">
@@ -5581,13 +5361,10 @@
       </c>
       <c r="J85" s="9" t="n"/>
       <c r="K85" s="10" t="inlineStr"/>
-      <c r="L85" s="11" t="n"/>
-      <c r="M85" s="11" t="n"/>
-      <c r="N85" s="11" t="n"/>
-      <c r="O85" s="11" t="n"/>
-      <c r="P85" s="11" t="n"/>
-      <c r="Q85" s="9" t="n"/>
-      <c r="R85" s="22" t="n"/>
+      <c r="L85" s="9" t="n"/>
+      <c r="M85" s="9" t="n"/>
+      <c r="N85" s="9" t="n"/>
+      <c r="O85" s="22" t="n"/>
     </row>
     <row r="86" ht="22" customHeight="1">
       <c r="A86" s="12" t="n">
@@ -5635,13 +5412,10 @@
       </c>
       <c r="J86" s="13" t="n"/>
       <c r="K86" s="14" t="inlineStr"/>
-      <c r="L86" s="15" t="n"/>
-      <c r="M86" s="15" t="n"/>
-      <c r="N86" s="15" t="n"/>
-      <c r="O86" s="15" t="n"/>
-      <c r="P86" s="15" t="n"/>
-      <c r="Q86" s="13" t="n"/>
-      <c r="R86" s="24" t="n"/>
+      <c r="L86" s="13" t="n"/>
+      <c r="M86" s="13" t="n"/>
+      <c r="N86" s="13" t="n"/>
+      <c r="O86" s="24" t="n"/>
     </row>
     <row r="87" ht="22" customHeight="1">
       <c r="A87" s="8" t="n">
@@ -5689,13 +5463,10 @@
       </c>
       <c r="J87" s="9" t="n"/>
       <c r="K87" s="10" t="inlineStr"/>
-      <c r="L87" s="11" t="n"/>
-      <c r="M87" s="11" t="n"/>
-      <c r="N87" s="11" t="n"/>
-      <c r="O87" s="11" t="n"/>
-      <c r="P87" s="11" t="n"/>
-      <c r="Q87" s="9" t="n"/>
-      <c r="R87" s="22" t="n"/>
+      <c r="L87" s="9" t="n"/>
+      <c r="M87" s="9" t="n"/>
+      <c r="N87" s="9" t="n"/>
+      <c r="O87" s="22" t="n"/>
     </row>
     <row r="88" ht="22" customHeight="1">
       <c r="A88" s="12" t="n">
@@ -5743,13 +5514,10 @@
       </c>
       <c r="J88" s="13" t="n"/>
       <c r="K88" s="14" t="inlineStr"/>
-      <c r="L88" s="15" t="n"/>
-      <c r="M88" s="15" t="n"/>
-      <c r="N88" s="15" t="n"/>
-      <c r="O88" s="15" t="n"/>
-      <c r="P88" s="15" t="n"/>
-      <c r="Q88" s="13" t="n"/>
-      <c r="R88" s="24" t="n"/>
+      <c r="L88" s="13" t="n"/>
+      <c r="M88" s="13" t="n"/>
+      <c r="N88" s="13" t="n"/>
+      <c r="O88" s="24" t="n"/>
     </row>
     <row r="89" ht="22" customHeight="1">
       <c r="A89" s="8" t="n">
@@ -5797,13 +5565,10 @@
       </c>
       <c r="J89" s="9" t="n"/>
       <c r="K89" s="10" t="inlineStr"/>
-      <c r="L89" s="11" t="n"/>
-      <c r="M89" s="11" t="n"/>
-      <c r="N89" s="11" t="n"/>
-      <c r="O89" s="11" t="n"/>
-      <c r="P89" s="11" t="n"/>
-      <c r="Q89" s="9" t="n"/>
-      <c r="R89" s="22" t="n"/>
+      <c r="L89" s="9" t="n"/>
+      <c r="M89" s="9" t="n"/>
+      <c r="N89" s="9" t="n"/>
+      <c r="O89" s="22" t="n"/>
     </row>
     <row r="90" ht="22" customHeight="1">
       <c r="A90" s="12" t="n">
@@ -5851,13 +5616,10 @@
       </c>
       <c r="J90" s="13" t="n"/>
       <c r="K90" s="14" t="inlineStr"/>
-      <c r="L90" s="15" t="n"/>
-      <c r="M90" s="15" t="n"/>
-      <c r="N90" s="15" t="n"/>
-      <c r="O90" s="15" t="n"/>
-      <c r="P90" s="15" t="n"/>
-      <c r="Q90" s="13" t="n"/>
-      <c r="R90" s="24" t="n"/>
+      <c r="L90" s="13" t="n"/>
+      <c r="M90" s="13" t="n"/>
+      <c r="N90" s="13" t="n"/>
+      <c r="O90" s="24" t="n"/>
     </row>
     <row r="91" ht="22" customHeight="1">
       <c r="A91" s="8" t="n">
@@ -5905,13 +5667,10 @@
       </c>
       <c r="J91" s="9" t="n"/>
       <c r="K91" s="10" t="inlineStr"/>
-      <c r="L91" s="11" t="n"/>
-      <c r="M91" s="11" t="n"/>
-      <c r="N91" s="11" t="n"/>
-      <c r="O91" s="11" t="n"/>
-      <c r="P91" s="11" t="n"/>
-      <c r="Q91" s="9" t="n"/>
-      <c r="R91" s="22" t="n"/>
+      <c r="L91" s="9" t="n"/>
+      <c r="M91" s="9" t="n"/>
+      <c r="N91" s="9" t="n"/>
+      <c r="O91" s="22" t="n"/>
     </row>
     <row r="92" ht="22" customHeight="1">
       <c r="A92" s="12" t="n">
@@ -5959,13 +5718,10 @@
       </c>
       <c r="J92" s="13" t="n"/>
       <c r="K92" s="14" t="inlineStr"/>
-      <c r="L92" s="15" t="n"/>
-      <c r="M92" s="15" t="n"/>
-      <c r="N92" s="15" t="n"/>
-      <c r="O92" s="15" t="n"/>
-      <c r="P92" s="15" t="n"/>
-      <c r="Q92" s="13" t="n"/>
-      <c r="R92" s="24" t="n"/>
+      <c r="L92" s="13" t="n"/>
+      <c r="M92" s="13" t="n"/>
+      <c r="N92" s="13" t="n"/>
+      <c r="O92" s="24" t="n"/>
     </row>
     <row r="93" ht="22" customHeight="1">
       <c r="A93" s="8" t="n">
@@ -6013,13 +5769,10 @@
       </c>
       <c r="J93" s="9" t="n"/>
       <c r="K93" s="10" t="inlineStr"/>
-      <c r="L93" s="11" t="n"/>
-      <c r="M93" s="11" t="n"/>
-      <c r="N93" s="11" t="n"/>
-      <c r="O93" s="11" t="n"/>
-      <c r="P93" s="11" t="n"/>
-      <c r="Q93" s="9" t="n"/>
-      <c r="R93" s="22" t="n"/>
+      <c r="L93" s="9" t="n"/>
+      <c r="M93" s="9" t="n"/>
+      <c r="N93" s="9" t="n"/>
+      <c r="O93" s="22" t="n"/>
     </row>
     <row r="94" ht="22" customHeight="1">
       <c r="A94" s="12" t="n">
@@ -6067,13 +5820,10 @@
       </c>
       <c r="J94" s="13" t="n"/>
       <c r="K94" s="14" t="inlineStr"/>
-      <c r="L94" s="15" t="n"/>
-      <c r="M94" s="15" t="n"/>
-      <c r="N94" s="15" t="n"/>
-      <c r="O94" s="15" t="n"/>
-      <c r="P94" s="15" t="n"/>
-      <c r="Q94" s="13" t="n"/>
-      <c r="R94" s="24" t="n"/>
+      <c r="L94" s="13" t="n"/>
+      <c r="M94" s="13" t="n"/>
+      <c r="N94" s="13" t="n"/>
+      <c r="O94" s="24" t="n"/>
     </row>
     <row r="95" ht="22" customHeight="1">
       <c r="A95" s="8" t="n">
@@ -6121,13 +5871,10 @@
       </c>
       <c r="J95" s="9" t="n"/>
       <c r="K95" s="10" t="inlineStr"/>
-      <c r="L95" s="11" t="n"/>
-      <c r="M95" s="11" t="n"/>
-      <c r="N95" s="11" t="n"/>
-      <c r="O95" s="11" t="n"/>
-      <c r="P95" s="11" t="n"/>
-      <c r="Q95" s="9" t="n"/>
-      <c r="R95" s="22" t="n"/>
+      <c r="L95" s="9" t="n"/>
+      <c r="M95" s="9" t="n"/>
+      <c r="N95" s="9" t="n"/>
+      <c r="O95" s="22" t="n"/>
     </row>
     <row r="96" ht="22" customHeight="1">
       <c r="A96" s="12" t="n">
@@ -6175,13 +5922,10 @@
       </c>
       <c r="J96" s="13" t="n"/>
       <c r="K96" s="14" t="inlineStr"/>
-      <c r="L96" s="15" t="n"/>
-      <c r="M96" s="15" t="n"/>
-      <c r="N96" s="15" t="n"/>
-      <c r="O96" s="15" t="n"/>
-      <c r="P96" s="15" t="n"/>
-      <c r="Q96" s="13" t="n"/>
-      <c r="R96" s="24" t="n"/>
+      <c r="L96" s="13" t="n"/>
+      <c r="M96" s="13" t="n"/>
+      <c r="N96" s="13" t="n"/>
+      <c r="O96" s="24" t="n"/>
     </row>
     <row r="97" ht="22" customHeight="1">
       <c r="A97" s="8" t="n">
@@ -6229,13 +5973,10 @@
       </c>
       <c r="J97" s="9" t="n"/>
       <c r="K97" s="10" t="inlineStr"/>
-      <c r="L97" s="11" t="n"/>
-      <c r="M97" s="11" t="n"/>
-      <c r="N97" s="11" t="n"/>
-      <c r="O97" s="11" t="n"/>
-      <c r="P97" s="11" t="n"/>
-      <c r="Q97" s="9" t="n"/>
-      <c r="R97" s="22" t="n"/>
+      <c r="L97" s="9" t="n"/>
+      <c r="M97" s="9" t="n"/>
+      <c r="N97" s="9" t="n"/>
+      <c r="O97" s="22" t="n"/>
     </row>
     <row r="98" ht="22" customHeight="1">
       <c r="A98" s="12" t="n">
@@ -6283,13 +6024,10 @@
       </c>
       <c r="J98" s="13" t="n"/>
       <c r="K98" s="14" t="inlineStr"/>
-      <c r="L98" s="15" t="n"/>
-      <c r="M98" s="15" t="n"/>
-      <c r="N98" s="15" t="n"/>
-      <c r="O98" s="15" t="n"/>
-      <c r="P98" s="15" t="n"/>
-      <c r="Q98" s="13" t="n"/>
-      <c r="R98" s="24" t="n"/>
+      <c r="L98" s="13" t="n"/>
+      <c r="M98" s="13" t="n"/>
+      <c r="N98" s="13" t="n"/>
+      <c r="O98" s="24" t="n"/>
     </row>
     <row r="99" ht="22" customHeight="1">
       <c r="A99" s="8" t="n">
@@ -6337,13 +6075,10 @@
       </c>
       <c r="J99" s="9" t="n"/>
       <c r="K99" s="10" t="inlineStr"/>
-      <c r="L99" s="11" t="n"/>
-      <c r="M99" s="11" t="n"/>
-      <c r="N99" s="11" t="n"/>
-      <c r="O99" s="11" t="n"/>
-      <c r="P99" s="11" t="n"/>
-      <c r="Q99" s="9" t="n"/>
-      <c r="R99" s="22" t="n"/>
+      <c r="L99" s="9" t="n"/>
+      <c r="M99" s="9" t="n"/>
+      <c r="N99" s="9" t="n"/>
+      <c r="O99" s="22" t="n"/>
     </row>
     <row r="100" ht="22" customHeight="1">
       <c r="A100" s="12" t="n">
@@ -6391,13 +6126,10 @@
       </c>
       <c r="J100" s="13" t="n"/>
       <c r="K100" s="14" t="inlineStr"/>
-      <c r="L100" s="15" t="n"/>
-      <c r="M100" s="15" t="n"/>
-      <c r="N100" s="15" t="n"/>
-      <c r="O100" s="15" t="n"/>
-      <c r="P100" s="15" t="n"/>
-      <c r="Q100" s="13" t="n"/>
-      <c r="R100" s="24" t="n"/>
+      <c r="L100" s="13" t="n"/>
+      <c r="M100" s="13" t="n"/>
+      <c r="N100" s="13" t="n"/>
+      <c r="O100" s="24" t="n"/>
     </row>
     <row r="101" ht="22" customHeight="1">
       <c r="A101" s="8" t="n">
@@ -6445,13 +6177,10 @@
       </c>
       <c r="J101" s="9" t="n"/>
       <c r="K101" s="10" t="inlineStr"/>
-      <c r="L101" s="11" t="n"/>
-      <c r="M101" s="11" t="n"/>
-      <c r="N101" s="11" t="n"/>
-      <c r="O101" s="11" t="n"/>
-      <c r="P101" s="11" t="n"/>
-      <c r="Q101" s="9" t="n"/>
-      <c r="R101" s="22" t="n"/>
+      <c r="L101" s="9" t="n"/>
+      <c r="M101" s="9" t="n"/>
+      <c r="N101" s="9" t="n"/>
+      <c r="O101" s="22" t="n"/>
     </row>
     <row r="102" ht="22" customHeight="1">
       <c r="A102" s="12" t="n">
@@ -6499,13 +6228,10 @@
       </c>
       <c r="J102" s="13" t="n"/>
       <c r="K102" s="14" t="inlineStr"/>
-      <c r="L102" s="15" t="n"/>
-      <c r="M102" s="15" t="n"/>
-      <c r="N102" s="15" t="n"/>
-      <c r="O102" s="15" t="n"/>
-      <c r="P102" s="15" t="n"/>
-      <c r="Q102" s="13" t="n"/>
-      <c r="R102" s="24" t="n"/>
+      <c r="L102" s="13" t="n"/>
+      <c r="M102" s="13" t="n"/>
+      <c r="N102" s="13" t="n"/>
+      <c r="O102" s="24" t="n"/>
     </row>
     <row r="103" ht="22" customHeight="1">
       <c r="A103" s="8" t="n">
@@ -6553,13 +6279,10 @@
       </c>
       <c r="J103" s="9" t="n"/>
       <c r="K103" s="10" t="inlineStr"/>
-      <c r="L103" s="11" t="n"/>
-      <c r="M103" s="11" t="n"/>
-      <c r="N103" s="11" t="n"/>
-      <c r="O103" s="11" t="n"/>
-      <c r="P103" s="11" t="n"/>
-      <c r="Q103" s="9" t="n"/>
-      <c r="R103" s="22" t="n"/>
+      <c r="L103" s="9" t="n"/>
+      <c r="M103" s="9" t="n"/>
+      <c r="N103" s="9" t="n"/>
+      <c r="O103" s="22" t="n"/>
     </row>
     <row r="104" ht="22" customHeight="1">
       <c r="A104" s="12" t="n">
@@ -6607,13 +6330,10 @@
       </c>
       <c r="J104" s="13" t="n"/>
       <c r="K104" s="14" t="inlineStr"/>
-      <c r="L104" s="15" t="n"/>
-      <c r="M104" s="15" t="n"/>
-      <c r="N104" s="15" t="n"/>
-      <c r="O104" s="15" t="n"/>
-      <c r="P104" s="15" t="n"/>
-      <c r="Q104" s="13" t="n"/>
-      <c r="R104" s="24" t="n"/>
+      <c r="L104" s="13" t="n"/>
+      <c r="M104" s="13" t="n"/>
+      <c r="N104" s="13" t="n"/>
+      <c r="O104" s="24" t="n"/>
     </row>
     <row r="105" ht="22" customHeight="1">
       <c r="A105" s="8" t="n">
@@ -6661,13 +6381,10 @@
       </c>
       <c r="J105" s="9" t="n"/>
       <c r="K105" s="10" t="inlineStr"/>
-      <c r="L105" s="11" t="n"/>
-      <c r="M105" s="11" t="n"/>
-      <c r="N105" s="11" t="n"/>
-      <c r="O105" s="11" t="n"/>
-      <c r="P105" s="11" t="n"/>
-      <c r="Q105" s="9" t="n"/>
-      <c r="R105" s="22" t="n"/>
+      <c r="L105" s="9" t="n"/>
+      <c r="M105" s="9" t="n"/>
+      <c r="N105" s="9" t="n"/>
+      <c r="O105" s="22" t="n"/>
     </row>
     <row r="106" ht="22" customHeight="1">
       <c r="A106" s="12" t="n">
@@ -6715,13 +6432,10 @@
       </c>
       <c r="J106" s="13" t="n"/>
       <c r="K106" s="14" t="inlineStr"/>
-      <c r="L106" s="15" t="n"/>
-      <c r="M106" s="15" t="n"/>
-      <c r="N106" s="15" t="n"/>
-      <c r="O106" s="15" t="n"/>
-      <c r="P106" s="15" t="n"/>
-      <c r="Q106" s="13" t="n"/>
-      <c r="R106" s="24" t="n"/>
+      <c r="L106" s="13" t="n"/>
+      <c r="M106" s="13" t="n"/>
+      <c r="N106" s="13" t="n"/>
+      <c r="O106" s="24" t="n"/>
     </row>
     <row r="107" ht="22" customHeight="1">
       <c r="A107" s="8" t="n">
@@ -6769,13 +6483,10 @@
       </c>
       <c r="J107" s="9" t="n"/>
       <c r="K107" s="10" t="inlineStr"/>
-      <c r="L107" s="11" t="n"/>
-      <c r="M107" s="11" t="n"/>
-      <c r="N107" s="11" t="n"/>
-      <c r="O107" s="11" t="n"/>
-      <c r="P107" s="11" t="n"/>
-      <c r="Q107" s="9" t="n"/>
-      <c r="R107" s="22" t="n"/>
+      <c r="L107" s="9" t="n"/>
+      <c r="M107" s="9" t="n"/>
+      <c r="N107" s="9" t="n"/>
+      <c r="O107" s="22" t="n"/>
     </row>
     <row r="108" ht="22" customHeight="1">
       <c r="A108" s="12" t="n">
@@ -6823,13 +6534,10 @@
       </c>
       <c r="J108" s="13" t="n"/>
       <c r="K108" s="14" t="inlineStr"/>
-      <c r="L108" s="15" t="n"/>
-      <c r="M108" s="15" t="n"/>
-      <c r="N108" s="15" t="n"/>
-      <c r="O108" s="15" t="n"/>
-      <c r="P108" s="15" t="n"/>
-      <c r="Q108" s="13" t="n"/>
-      <c r="R108" s="24" t="n"/>
+      <c r="L108" s="13" t="n"/>
+      <c r="M108" s="13" t="n"/>
+      <c r="N108" s="13" t="n"/>
+      <c r="O108" s="24" t="n"/>
     </row>
     <row r="109" ht="22" customHeight="1">
       <c r="A109" s="8" t="n">
@@ -6876,10 +6584,7 @@
       <c r="L109" s="9" t="n"/>
       <c r="M109" s="9" t="n"/>
       <c r="N109" s="9" t="n"/>
-      <c r="O109" s="9" t="n"/>
-      <c r="P109" s="9" t="n"/>
-      <c r="Q109" s="9" t="n"/>
-      <c r="R109" s="22" t="n"/>
+      <c r="O109" s="22" t="n"/>
     </row>
     <row r="110" ht="22" customHeight="1">
       <c r="A110" s="12" t="n">
@@ -6918,10 +6623,7 @@
       <c r="L110" s="13" t="n"/>
       <c r="M110" s="13" t="n"/>
       <c r="N110" s="13" t="n"/>
-      <c r="O110" s="13" t="n"/>
-      <c r="P110" s="13" t="n"/>
-      <c r="Q110" s="13" t="n"/>
-      <c r="R110" s="24" t="n"/>
+      <c r="O110" s="24" t="n"/>
     </row>
     <row r="111" ht="22" customHeight="1">
       <c r="A111" s="8" t="n"/>
@@ -6938,10 +6640,7 @@
       <c r="L111" s="9" t="n"/>
       <c r="M111" s="9" t="n"/>
       <c r="N111" s="9" t="n"/>
-      <c r="O111" s="9" t="n"/>
-      <c r="P111" s="9" t="n"/>
-      <c r="Q111" s="9" t="n"/>
-      <c r="R111" s="22" t="n"/>
+      <c r="O111" s="22" t="n"/>
     </row>
     <row r="112" ht="22" customHeight="1">
       <c r="A112" s="12" t="n"/>
@@ -6958,10 +6657,7 @@
       <c r="L112" s="13" t="n"/>
       <c r="M112" s="13" t="n"/>
       <c r="N112" s="13" t="n"/>
-      <c r="O112" s="13" t="n"/>
-      <c r="P112" s="13" t="n"/>
-      <c r="Q112" s="13" t="n"/>
-      <c r="R112" s="24" t="n"/>
+      <c r="O112" s="24" t="n"/>
     </row>
     <row r="113" ht="22" customHeight="1">
       <c r="A113" s="8" t="n"/>
@@ -6978,10 +6674,7 @@
       <c r="L113" s="9" t="n"/>
       <c r="M113" s="9" t="n"/>
       <c r="N113" s="9" t="n"/>
-      <c r="O113" s="9" t="n"/>
-      <c r="P113" s="9" t="n"/>
-      <c r="Q113" s="9" t="n"/>
-      <c r="R113" s="22" t="n"/>
+      <c r="O113" s="22" t="n"/>
     </row>
     <row r="114" ht="22" customHeight="1">
       <c r="A114" s="12" t="n"/>
@@ -6998,10 +6691,7 @@
       <c r="L114" s="13" t="n"/>
       <c r="M114" s="13" t="n"/>
       <c r="N114" s="13" t="n"/>
-      <c r="O114" s="13" t="n"/>
-      <c r="P114" s="13" t="n"/>
-      <c r="Q114" s="13" t="n"/>
-      <c r="R114" s="24" t="n"/>
+      <c r="O114" s="24" t="n"/>
     </row>
     <row r="115" ht="22" customHeight="1">
       <c r="A115" s="8" t="n"/>
@@ -7018,10 +6708,7 @@
       <c r="L115" s="9" t="n"/>
       <c r="M115" s="9" t="n"/>
       <c r="N115" s="9" t="n"/>
-      <c r="O115" s="9" t="n"/>
-      <c r="P115" s="9" t="n"/>
-      <c r="Q115" s="9" t="n"/>
-      <c r="R115" s="22" t="n"/>
+      <c r="O115" s="22" t="n"/>
     </row>
     <row r="116" ht="22" customHeight="1">
       <c r="A116" s="12" t="n"/>
@@ -7038,10 +6725,7 @@
       <c r="L116" s="13" t="n"/>
       <c r="M116" s="13" t="n"/>
       <c r="N116" s="13" t="n"/>
-      <c r="O116" s="13" t="n"/>
-      <c r="P116" s="13" t="n"/>
-      <c r="Q116" s="13" t="n"/>
-      <c r="R116" s="24" t="n"/>
+      <c r="O116" s="24" t="n"/>
     </row>
     <row r="117" ht="22" customHeight="1">
       <c r="A117" s="8" t="n"/>
@@ -7058,10 +6742,7 @@
       <c r="L117" s="9" t="n"/>
       <c r="M117" s="9" t="n"/>
       <c r="N117" s="9" t="n"/>
-      <c r="O117" s="9" t="n"/>
-      <c r="P117" s="9" t="n"/>
-      <c r="Q117" s="9" t="n"/>
-      <c r="R117" s="22" t="n"/>
+      <c r="O117" s="22" t="n"/>
     </row>
     <row r="118" ht="22" customHeight="1">
       <c r="A118" s="12" t="n"/>
@@ -7078,10 +6759,7 @@
       <c r="L118" s="13" t="n"/>
       <c r="M118" s="13" t="n"/>
       <c r="N118" s="13" t="n"/>
-      <c r="O118" s="13" t="n"/>
-      <c r="P118" s="13" t="n"/>
-      <c r="Q118" s="13" t="n"/>
-      <c r="R118" s="24" t="n"/>
+      <c r="O118" s="24" t="n"/>
     </row>
     <row r="119" ht="22" customHeight="1">
       <c r="A119" s="8" t="n"/>
@@ -7098,10 +6776,7 @@
       <c r="L119" s="9" t="n"/>
       <c r="M119" s="9" t="n"/>
       <c r="N119" s="9" t="n"/>
-      <c r="O119" s="9" t="n"/>
-      <c r="P119" s="9" t="n"/>
-      <c r="Q119" s="9" t="n"/>
-      <c r="R119" s="22" t="n"/>
+      <c r="O119" s="22" t="n"/>
     </row>
     <row r="120" ht="22" customHeight="1">
       <c r="A120" s="12" t="n"/>
@@ -7118,10 +6793,7 @@
       <c r="L120" s="13" t="n"/>
       <c r="M120" s="13" t="n"/>
       <c r="N120" s="13" t="n"/>
-      <c r="O120" s="13" t="n"/>
-      <c r="P120" s="13" t="n"/>
-      <c r="Q120" s="13" t="n"/>
-      <c r="R120" s="24" t="n"/>
+      <c r="O120" s="24" t="n"/>
     </row>
     <row r="121" ht="22" customHeight="1">
       <c r="A121" s="8" t="n"/>
@@ -7138,10 +6810,7 @@
       <c r="L121" s="9" t="n"/>
       <c r="M121" s="9" t="n"/>
       <c r="N121" s="9" t="n"/>
-      <c r="O121" s="9" t="n"/>
-      <c r="P121" s="9" t="n"/>
-      <c r="Q121" s="9" t="n"/>
-      <c r="R121" s="22" t="n"/>
+      <c r="O121" s="22" t="n"/>
     </row>
     <row r="122" ht="22" customHeight="1">
       <c r="A122" s="12" t="n"/>
@@ -7158,10 +6827,7 @@
       <c r="L122" s="13" t="n"/>
       <c r="M122" s="13" t="n"/>
       <c r="N122" s="13" t="n"/>
-      <c r="O122" s="13" t="n"/>
-      <c r="P122" s="13" t="n"/>
-      <c r="Q122" s="13" t="n"/>
-      <c r="R122" s="24" t="n"/>
+      <c r="O122" s="24" t="n"/>
     </row>
     <row r="123" ht="22" customHeight="1">
       <c r="A123" s="8" t="n"/>
@@ -7178,10 +6844,7 @@
       <c r="L123" s="9" t="n"/>
       <c r="M123" s="9" t="n"/>
       <c r="N123" s="9" t="n"/>
-      <c r="O123" s="9" t="n"/>
-      <c r="P123" s="9" t="n"/>
-      <c r="Q123" s="9" t="n"/>
-      <c r="R123" s="22" t="n"/>
+      <c r="O123" s="22" t="n"/>
     </row>
     <row r="124" ht="22" customHeight="1">
       <c r="A124" s="12" t="n"/>
@@ -7198,10 +6861,7 @@
       <c r="L124" s="13" t="n"/>
       <c r="M124" s="13" t="n"/>
       <c r="N124" s="13" t="n"/>
-      <c r="O124" s="13" t="n"/>
-      <c r="P124" s="13" t="n"/>
-      <c r="Q124" s="13" t="n"/>
-      <c r="R124" s="24" t="n"/>
+      <c r="O124" s="24" t="n"/>
     </row>
     <row r="125" ht="22" customHeight="1">
       <c r="A125" s="8" t="n"/>
@@ -7218,10 +6878,7 @@
       <c r="L125" s="9" t="n"/>
       <c r="M125" s="9" t="n"/>
       <c r="N125" s="9" t="n"/>
-      <c r="O125" s="9" t="n"/>
-      <c r="P125" s="9" t="n"/>
-      <c r="Q125" s="9" t="n"/>
-      <c r="R125" s="22" t="n"/>
+      <c r="O125" s="22" t="n"/>
     </row>
     <row r="126" ht="22" customHeight="1">
       <c r="A126" s="12" t="n"/>
@@ -7238,10 +6895,7 @@
       <c r="L126" s="13" t="n"/>
       <c r="M126" s="13" t="n"/>
       <c r="N126" s="13" t="n"/>
-      <c r="O126" s="13" t="n"/>
-      <c r="P126" s="13" t="n"/>
-      <c r="Q126" s="13" t="n"/>
-      <c r="R126" s="24" t="n"/>
+      <c r="O126" s="24" t="n"/>
     </row>
     <row r="127" ht="22" customHeight="1">
       <c r="A127" s="8" t="n"/>
@@ -7258,10 +6912,7 @@
       <c r="L127" s="9" t="n"/>
       <c r="M127" s="9" t="n"/>
       <c r="N127" s="9" t="n"/>
-      <c r="O127" s="9" t="n"/>
-      <c r="P127" s="9" t="n"/>
-      <c r="Q127" s="9" t="n"/>
-      <c r="R127" s="22" t="n"/>
+      <c r="O127" s="22" t="n"/>
     </row>
     <row r="128" ht="22" customHeight="1">
       <c r="A128" s="12" t="n"/>
@@ -7278,10 +6929,7 @@
       <c r="L128" s="13" t="n"/>
       <c r="M128" s="13" t="n"/>
       <c r="N128" s="13" t="n"/>
-      <c r="O128" s="13" t="n"/>
-      <c r="P128" s="13" t="n"/>
-      <c r="Q128" s="13" t="n"/>
-      <c r="R128" s="24" t="n"/>
+      <c r="O128" s="24" t="n"/>
     </row>
     <row r="129" ht="22" customHeight="1">
       <c r="A129" s="8" t="n"/>
@@ -7298,10 +6946,7 @@
       <c r="L129" s="9" t="n"/>
       <c r="M129" s="9" t="n"/>
       <c r="N129" s="9" t="n"/>
-      <c r="O129" s="9" t="n"/>
-      <c r="P129" s="9" t="n"/>
-      <c r="Q129" s="9" t="n"/>
-      <c r="R129" s="22" t="n"/>
+      <c r="O129" s="22" t="n"/>
     </row>
     <row r="130" ht="22" customHeight="1">
       <c r="A130" s="12" t="n"/>
@@ -7318,10 +6963,7 @@
       <c r="L130" s="13" t="n"/>
       <c r="M130" s="13" t="n"/>
       <c r="N130" s="13" t="n"/>
-      <c r="O130" s="13" t="n"/>
-      <c r="P130" s="13" t="n"/>
-      <c r="Q130" s="13" t="n"/>
-      <c r="R130" s="24" t="n"/>
+      <c r="O130" s="24" t="n"/>
     </row>
     <row r="131" ht="22" customHeight="1">
       <c r="A131" s="8" t="n"/>
@@ -7338,10 +6980,7 @@
       <c r="L131" s="9" t="n"/>
       <c r="M131" s="9" t="n"/>
       <c r="N131" s="9" t="n"/>
-      <c r="O131" s="9" t="n"/>
-      <c r="P131" s="9" t="n"/>
-      <c r="Q131" s="9" t="n"/>
-      <c r="R131" s="22" t="n"/>
+      <c r="O131" s="22" t="n"/>
     </row>
     <row r="132" ht="22" customHeight="1">
       <c r="A132" s="12" t="n"/>
@@ -7358,10 +6997,7 @@
       <c r="L132" s="13" t="n"/>
       <c r="M132" s="13" t="n"/>
       <c r="N132" s="13" t="n"/>
-      <c r="O132" s="13" t="n"/>
-      <c r="P132" s="13" t="n"/>
-      <c r="Q132" s="13" t="n"/>
-      <c r="R132" s="24" t="n"/>
+      <c r="O132" s="24" t="n"/>
     </row>
     <row r="133" ht="22" customHeight="1">
       <c r="A133" s="8" t="n"/>
@@ -7378,10 +7014,7 @@
       <c r="L133" s="9" t="n"/>
       <c r="M133" s="9" t="n"/>
       <c r="N133" s="9" t="n"/>
-      <c r="O133" s="9" t="n"/>
-      <c r="P133" s="9" t="n"/>
-      <c r="Q133" s="9" t="n"/>
-      <c r="R133" s="22" t="n"/>
+      <c r="O133" s="22" t="n"/>
     </row>
     <row r="134" ht="22" customHeight="1">
       <c r="A134" s="12" t="n"/>
@@ -7398,10 +7031,7 @@
       <c r="L134" s="13" t="n"/>
       <c r="M134" s="13" t="n"/>
       <c r="N134" s="13" t="n"/>
-      <c r="O134" s="13" t="n"/>
-      <c r="P134" s="13" t="n"/>
-      <c r="Q134" s="13" t="n"/>
-      <c r="R134" s="24" t="n"/>
+      <c r="O134" s="24" t="n"/>
     </row>
     <row r="135" ht="22" customHeight="1">
       <c r="A135" s="8" t="n"/>
@@ -7418,10 +7048,7 @@
       <c r="L135" s="9" t="n"/>
       <c r="M135" s="9" t="n"/>
       <c r="N135" s="9" t="n"/>
-      <c r="O135" s="9" t="n"/>
-      <c r="P135" s="9" t="n"/>
-      <c r="Q135" s="9" t="n"/>
-      <c r="R135" s="22" t="n"/>
+      <c r="O135" s="22" t="n"/>
     </row>
     <row r="136" ht="22" customHeight="1">
       <c r="A136" s="12" t="n"/>
@@ -7438,10 +7065,7 @@
       <c r="L136" s="13" t="n"/>
       <c r="M136" s="13" t="n"/>
       <c r="N136" s="13" t="n"/>
-      <c r="O136" s="13" t="n"/>
-      <c r="P136" s="13" t="n"/>
-      <c r="Q136" s="13" t="n"/>
-      <c r="R136" s="24" t="n"/>
+      <c r="O136" s="24" t="n"/>
     </row>
     <row r="137" ht="22" customHeight="1">
       <c r="A137" s="8" t="n"/>
@@ -7458,10 +7082,7 @@
       <c r="L137" s="9" t="n"/>
       <c r="M137" s="9" t="n"/>
       <c r="N137" s="9" t="n"/>
-      <c r="O137" s="9" t="n"/>
-      <c r="P137" s="9" t="n"/>
-      <c r="Q137" s="9" t="n"/>
-      <c r="R137" s="22" t="n"/>
+      <c r="O137" s="22" t="n"/>
     </row>
     <row r="138" ht="22" customHeight="1">
       <c r="A138" s="12" t="n"/>
@@ -7478,10 +7099,7 @@
       <c r="L138" s="13" t="n"/>
       <c r="M138" s="13" t="n"/>
       <c r="N138" s="13" t="n"/>
-      <c r="O138" s="13" t="n"/>
-      <c r="P138" s="13" t="n"/>
-      <c r="Q138" s="13" t="n"/>
-      <c r="R138" s="24" t="n"/>
+      <c r="O138" s="24" t="n"/>
     </row>
     <row r="139" ht="22" customHeight="1">
       <c r="A139" s="8" t="n"/>
@@ -7498,10 +7116,7 @@
       <c r="L139" s="9" t="n"/>
       <c r="M139" s="9" t="n"/>
       <c r="N139" s="9" t="n"/>
-      <c r="O139" s="9" t="n"/>
-      <c r="P139" s="9" t="n"/>
-      <c r="Q139" s="9" t="n"/>
-      <c r="R139" s="22" t="n"/>
+      <c r="O139" s="22" t="n"/>
     </row>
     <row r="140" ht="22" customHeight="1">
       <c r="A140" s="12" t="n"/>
@@ -7518,16 +7133,13 @@
       <c r="L140" s="13" t="n"/>
       <c r="M140" s="13" t="n"/>
       <c r="N140" s="13" t="n"/>
-      <c r="O140" s="13" t="n"/>
-      <c r="P140" s="13" t="n"/>
-      <c r="Q140" s="13" t="n"/>
-      <c r="R140" s="24" t="n"/>
+      <c r="O140" s="24" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="DEDA"/>
   <mergeCells count="2">
-    <mergeCell ref="A2:Q2"/>
-    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A2:N2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="Q5:Q109" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">

--- a/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_검사기팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_검사기팀_입력_2026.xlsx
@@ -214,7 +214,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -433,6 +433,15 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -660,11 +669,15 @@
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 전체 진척률(%)
-• 자동 계산 — 참여 부서 소계의 평균
-  예: 3개 부서 진척률 80/50/30 → 53%
-• sync 시 갱신, 수동 수정 불가
-• 100% = 전 부서 완료 상태</t>
+        <t>▣ 부서 진척률 (%) — 본인 부서 작업
+• 자동 계산 (수정 불가, sync 시 갱신)
+• 시작일·완료일 입력 기반:
+    0%  = 미착수    (시작일·완료일 모두 빈 칸)
+   50%  = 진행중    (시작일만 입력)
+  100%  = 완료      (완료일까지 입력)
+• ★ 이 값은 '이 부서'만의 진척률입니다.
+• 프로젝트 전체 진척률은 PMS 1_프로젝트등록
+  '진척률(%)' 컬럼에서 확인 (= 완료부서/참여부서)</t>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
@@ -1034,7 +1047,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="79" t="inlineStr">
+      <c r="A1" s="82" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 검사기팀 │ 2026</t>
         </is>
@@ -1055,7 +1068,7 @@
       <c r="O1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="80" t="inlineStr">
+      <c r="A2" s="83" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 검사기팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1073,9 +1086,9 @@
       <c r="L2" s="16" t="n"/>
       <c r="M2" s="16" t="n"/>
       <c r="N2" s="17" t="n"/>
-      <c r="O2" s="81" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 02:00</t>
+      <c r="O2" s="84" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 11:44</t>
         </is>
       </c>
     </row>
@@ -1209,7 +1222,7 @@
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>전체진척률(%)</t>
+          <t>부서진척률(%)</t>
         </is>
       </c>
       <c r="L4" s="72" t="inlineStr">
@@ -1280,7 +1293,9 @@
         </is>
       </c>
       <c r="J5" s="9" t="n"/>
-      <c r="K5" s="10" t="inlineStr"/>
+      <c r="K5" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L5" s="9" t="n"/>
       <c r="M5" s="9" t="n"/>
       <c r="N5" s="9" t="n"/>
@@ -1331,7 +1346,9 @@
         </is>
       </c>
       <c r="J6" s="13" t="n"/>
-      <c r="K6" s="14" t="inlineStr"/>
+      <c r="K6" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L6" s="13" t="n"/>
       <c r="M6" s="13" t="n"/>
       <c r="N6" s="13" t="n"/>
@@ -1382,7 +1399,9 @@
         </is>
       </c>
       <c r="J7" s="9" t="n"/>
-      <c r="K7" s="10" t="inlineStr"/>
+      <c r="K7" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L7" s="9" t="n"/>
       <c r="M7" s="9" t="n"/>
       <c r="N7" s="9" t="n"/>
@@ -1433,7 +1452,9 @@
         </is>
       </c>
       <c r="J8" s="13" t="n"/>
-      <c r="K8" s="14" t="inlineStr"/>
+      <c r="K8" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L8" s="13" t="n"/>
       <c r="M8" s="13" t="n"/>
       <c r="N8" s="13" t="n"/>
@@ -1484,7 +1505,9 @@
         </is>
       </c>
       <c r="J9" s="9" t="n"/>
-      <c r="K9" s="10" t="inlineStr"/>
+      <c r="K9" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L9" s="9" t="n"/>
       <c r="M9" s="9" t="n"/>
       <c r="N9" s="9" t="n"/>
@@ -1535,7 +1558,9 @@
         </is>
       </c>
       <c r="J10" s="13" t="n"/>
-      <c r="K10" s="14" t="inlineStr"/>
+      <c r="K10" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L10" s="13" t="n"/>
       <c r="M10" s="13" t="n"/>
       <c r="N10" s="13" t="n"/>
@@ -1586,7 +1611,9 @@
         </is>
       </c>
       <c r="J11" s="9" t="n"/>
-      <c r="K11" s="10" t="inlineStr"/>
+      <c r="K11" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L11" s="9" t="n"/>
       <c r="M11" s="9" t="n"/>
       <c r="N11" s="9" t="n"/>
@@ -1637,7 +1664,9 @@
         </is>
       </c>
       <c r="J12" s="13" t="n"/>
-      <c r="K12" s="14" t="inlineStr"/>
+      <c r="K12" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L12" s="13" t="n"/>
       <c r="M12" s="13" t="n"/>
       <c r="N12" s="13" t="n"/>
@@ -1688,7 +1717,9 @@
         </is>
       </c>
       <c r="J13" s="9" t="n"/>
-      <c r="K13" s="10" t="inlineStr"/>
+      <c r="K13" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L13" s="9" t="n"/>
       <c r="M13" s="9" t="n"/>
       <c r="N13" s="9" t="n"/>
@@ -1739,7 +1770,9 @@
         </is>
       </c>
       <c r="J14" s="13" t="n"/>
-      <c r="K14" s="14" t="inlineStr"/>
+      <c r="K14" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L14" s="13" t="n"/>
       <c r="M14" s="13" t="n"/>
       <c r="N14" s="13" t="n"/>
@@ -1790,7 +1823,9 @@
         </is>
       </c>
       <c r="J15" s="9" t="n"/>
-      <c r="K15" s="10" t="inlineStr"/>
+      <c r="K15" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L15" s="9" t="n"/>
       <c r="M15" s="9" t="n"/>
       <c r="N15" s="9" t="n"/>
@@ -1841,7 +1876,9 @@
         </is>
       </c>
       <c r="J16" s="13" t="n"/>
-      <c r="K16" s="14" t="inlineStr"/>
+      <c r="K16" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L16" s="13" t="n"/>
       <c r="M16" s="13" t="n"/>
       <c r="N16" s="13" t="n"/>
@@ -1892,7 +1929,9 @@
         </is>
       </c>
       <c r="J17" s="9" t="n"/>
-      <c r="K17" s="10" t="inlineStr"/>
+      <c r="K17" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L17" s="9" t="n"/>
       <c r="M17" s="9" t="n"/>
       <c r="N17" s="9" t="n"/>
@@ -1943,7 +1982,9 @@
         </is>
       </c>
       <c r="J18" s="13" t="n"/>
-      <c r="K18" s="14" t="inlineStr"/>
+      <c r="K18" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L18" s="13" t="n"/>
       <c r="M18" s="13" t="n"/>
       <c r="N18" s="13" t="n"/>
@@ -1994,7 +2035,9 @@
         </is>
       </c>
       <c r="J19" s="9" t="n"/>
-      <c r="K19" s="10" t="inlineStr"/>
+      <c r="K19" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L19" s="9" t="n"/>
       <c r="M19" s="9" t="n"/>
       <c r="N19" s="9" t="n"/>
@@ -2045,7 +2088,9 @@
         </is>
       </c>
       <c r="J20" s="13" t="n"/>
-      <c r="K20" s="14" t="inlineStr"/>
+      <c r="K20" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L20" s="13" t="n"/>
       <c r="M20" s="13" t="n"/>
       <c r="N20" s="13" t="n"/>
@@ -2096,7 +2141,9 @@
         </is>
       </c>
       <c r="J21" s="9" t="n"/>
-      <c r="K21" s="10" t="inlineStr"/>
+      <c r="K21" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L21" s="9" t="n"/>
       <c r="M21" s="9" t="n"/>
       <c r="N21" s="9" t="n"/>
@@ -2147,7 +2194,9 @@
         </is>
       </c>
       <c r="J22" s="13" t="n"/>
-      <c r="K22" s="14" t="inlineStr"/>
+      <c r="K22" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L22" s="13" t="n"/>
       <c r="M22" s="13" t="n"/>
       <c r="N22" s="13" t="n"/>
@@ -2198,7 +2247,9 @@
         </is>
       </c>
       <c r="J23" s="9" t="n"/>
-      <c r="K23" s="10" t="inlineStr"/>
+      <c r="K23" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L23" s="9" t="n"/>
       <c r="M23" s="9" t="n"/>
       <c r="N23" s="9" t="n"/>
@@ -2249,7 +2300,9 @@
         </is>
       </c>
       <c r="J24" s="13" t="n"/>
-      <c r="K24" s="14" t="inlineStr"/>
+      <c r="K24" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L24" s="13" t="n"/>
       <c r="M24" s="13" t="n"/>
       <c r="N24" s="13" t="n"/>
@@ -2300,7 +2353,9 @@
         </is>
       </c>
       <c r="J25" s="9" t="n"/>
-      <c r="K25" s="10" t="inlineStr"/>
+      <c r="K25" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L25" s="9" t="n"/>
       <c r="M25" s="9" t="n"/>
       <c r="N25" s="9" t="n"/>
@@ -2351,7 +2406,9 @@
         </is>
       </c>
       <c r="J26" s="13" t="n"/>
-      <c r="K26" s="14" t="inlineStr"/>
+      <c r="K26" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L26" s="13" t="n"/>
       <c r="M26" s="13" t="n"/>
       <c r="N26" s="13" t="n"/>
@@ -2402,7 +2459,9 @@
         </is>
       </c>
       <c r="J27" s="9" t="n"/>
-      <c r="K27" s="10" t="inlineStr"/>
+      <c r="K27" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L27" s="9" t="n"/>
       <c r="M27" s="9" t="n"/>
       <c r="N27" s="9" t="n"/>
@@ -2453,7 +2512,9 @@
         </is>
       </c>
       <c r="J28" s="13" t="n"/>
-      <c r="K28" s="14" t="inlineStr"/>
+      <c r="K28" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L28" s="13" t="n"/>
       <c r="M28" s="13" t="n"/>
       <c r="N28" s="13" t="n"/>
@@ -2504,7 +2565,9 @@
         </is>
       </c>
       <c r="J29" s="9" t="n"/>
-      <c r="K29" s="10" t="inlineStr"/>
+      <c r="K29" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L29" s="9" t="n"/>
       <c r="M29" s="9" t="n"/>
       <c r="N29" s="9" t="n"/>
@@ -2555,7 +2618,9 @@
         </is>
       </c>
       <c r="J30" s="13" t="n"/>
-      <c r="K30" s="14" t="inlineStr"/>
+      <c r="K30" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L30" s="13" t="n"/>
       <c r="M30" s="13" t="n"/>
       <c r="N30" s="13" t="n"/>
@@ -2606,7 +2671,9 @@
         </is>
       </c>
       <c r="J31" s="9" t="n"/>
-      <c r="K31" s="10" t="inlineStr"/>
+      <c r="K31" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L31" s="9" t="n"/>
       <c r="M31" s="9" t="n"/>
       <c r="N31" s="9" t="n"/>
@@ -2657,7 +2724,9 @@
         </is>
       </c>
       <c r="J32" s="13" t="n"/>
-      <c r="K32" s="14" t="inlineStr"/>
+      <c r="K32" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L32" s="13" t="n"/>
       <c r="M32" s="13" t="n"/>
       <c r="N32" s="13" t="n"/>
@@ -2708,7 +2777,9 @@
         </is>
       </c>
       <c r="J33" s="9" t="n"/>
-      <c r="K33" s="10" t="inlineStr"/>
+      <c r="K33" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L33" s="9" t="n"/>
       <c r="M33" s="9" t="n"/>
       <c r="N33" s="9" t="n"/>
@@ -2759,7 +2830,9 @@
         </is>
       </c>
       <c r="J34" s="13" t="n"/>
-      <c r="K34" s="14" t="inlineStr"/>
+      <c r="K34" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L34" s="13" t="n"/>
       <c r="M34" s="13" t="n"/>
       <c r="N34" s="13" t="n"/>
@@ -2810,7 +2883,9 @@
         </is>
       </c>
       <c r="J35" s="9" t="n"/>
-      <c r="K35" s="10" t="inlineStr"/>
+      <c r="K35" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L35" s="9" t="n"/>
       <c r="M35" s="9" t="n"/>
       <c r="N35" s="9" t="n"/>
@@ -2861,7 +2936,9 @@
         </is>
       </c>
       <c r="J36" s="13" t="n"/>
-      <c r="K36" s="14" t="inlineStr"/>
+      <c r="K36" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L36" s="13" t="n"/>
       <c r="M36" s="13" t="n"/>
       <c r="N36" s="13" t="n"/>
@@ -2912,7 +2989,9 @@
         </is>
       </c>
       <c r="J37" s="9" t="n"/>
-      <c r="K37" s="10" t="inlineStr"/>
+      <c r="K37" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L37" s="9" t="n"/>
       <c r="M37" s="9" t="n"/>
       <c r="N37" s="9" t="n"/>
@@ -2963,7 +3042,9 @@
         </is>
       </c>
       <c r="J38" s="13" t="n"/>
-      <c r="K38" s="14" t="inlineStr"/>
+      <c r="K38" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L38" s="13" t="n"/>
       <c r="M38" s="13" t="n"/>
       <c r="N38" s="13" t="n"/>
@@ -3014,7 +3095,9 @@
         </is>
       </c>
       <c r="J39" s="9" t="n"/>
-      <c r="K39" s="10" t="inlineStr"/>
+      <c r="K39" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L39" s="9" t="n"/>
       <c r="M39" s="9" t="n"/>
       <c r="N39" s="9" t="n"/>
@@ -3065,7 +3148,9 @@
         </is>
       </c>
       <c r="J40" s="13" t="n"/>
-      <c r="K40" s="14" t="inlineStr"/>
+      <c r="K40" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L40" s="13" t="n"/>
       <c r="M40" s="13" t="n"/>
       <c r="N40" s="13" t="n"/>
@@ -3116,7 +3201,9 @@
         </is>
       </c>
       <c r="J41" s="9" t="n"/>
-      <c r="K41" s="10" t="inlineStr"/>
+      <c r="K41" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L41" s="9" t="n"/>
       <c r="M41" s="9" t="n"/>
       <c r="N41" s="9" t="n"/>
@@ -3167,7 +3254,9 @@
         </is>
       </c>
       <c r="J42" s="13" t="n"/>
-      <c r="K42" s="14" t="inlineStr"/>
+      <c r="K42" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L42" s="13" t="n"/>
       <c r="M42" s="13" t="n"/>
       <c r="N42" s="13" t="n"/>
@@ -3218,7 +3307,9 @@
         </is>
       </c>
       <c r="J43" s="9" t="n"/>
-      <c r="K43" s="10" t="inlineStr"/>
+      <c r="K43" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L43" s="9" t="n"/>
       <c r="M43" s="9" t="n"/>
       <c r="N43" s="9" t="n"/>
@@ -3269,7 +3360,9 @@
         </is>
       </c>
       <c r="J44" s="13" t="n"/>
-      <c r="K44" s="14" t="inlineStr"/>
+      <c r="K44" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L44" s="13" t="n"/>
       <c r="M44" s="13" t="n"/>
       <c r="N44" s="13" t="n"/>
@@ -3320,7 +3413,9 @@
         </is>
       </c>
       <c r="J45" s="9" t="n"/>
-      <c r="K45" s="10" t="inlineStr"/>
+      <c r="K45" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L45" s="9" t="n"/>
       <c r="M45" s="9" t="n"/>
       <c r="N45" s="9" t="n"/>
@@ -3371,7 +3466,9 @@
         </is>
       </c>
       <c r="J46" s="13" t="n"/>
-      <c r="K46" s="14" t="inlineStr"/>
+      <c r="K46" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L46" s="13" t="n"/>
       <c r="M46" s="13" t="n"/>
       <c r="N46" s="13" t="n"/>
@@ -3422,7 +3519,9 @@
         </is>
       </c>
       <c r="J47" s="9" t="n"/>
-      <c r="K47" s="10" t="inlineStr"/>
+      <c r="K47" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L47" s="9" t="n"/>
       <c r="M47" s="9" t="n"/>
       <c r="N47" s="9" t="n"/>
@@ -3473,7 +3572,9 @@
         </is>
       </c>
       <c r="J48" s="13" t="n"/>
-      <c r="K48" s="14" t="inlineStr"/>
+      <c r="K48" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L48" s="13" t="n"/>
       <c r="M48" s="13" t="n"/>
       <c r="N48" s="13" t="n"/>
@@ -3524,7 +3625,9 @@
         </is>
       </c>
       <c r="J49" s="9" t="n"/>
-      <c r="K49" s="10" t="inlineStr"/>
+      <c r="K49" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L49" s="9" t="n"/>
       <c r="M49" s="9" t="n"/>
       <c r="N49" s="9" t="n"/>
@@ -3575,7 +3678,9 @@
         </is>
       </c>
       <c r="J50" s="13" t="n"/>
-      <c r="K50" s="14" t="inlineStr"/>
+      <c r="K50" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L50" s="13" t="n"/>
       <c r="M50" s="13" t="n"/>
       <c r="N50" s="13" t="n"/>
@@ -3626,7 +3731,9 @@
         </is>
       </c>
       <c r="J51" s="9" t="n"/>
-      <c r="K51" s="10" t="inlineStr"/>
+      <c r="K51" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L51" s="9" t="n"/>
       <c r="M51" s="9" t="n"/>
       <c r="N51" s="9" t="n"/>
@@ -3677,7 +3784,9 @@
         </is>
       </c>
       <c r="J52" s="13" t="n"/>
-      <c r="K52" s="14" t="inlineStr"/>
+      <c r="K52" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L52" s="13" t="n"/>
       <c r="M52" s="13" t="n"/>
       <c r="N52" s="13" t="n"/>
@@ -3728,7 +3837,9 @@
         </is>
       </c>
       <c r="J53" s="9" t="n"/>
-      <c r="K53" s="10" t="inlineStr"/>
+      <c r="K53" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L53" s="9" t="n"/>
       <c r="M53" s="9" t="n"/>
       <c r="N53" s="9" t="n"/>
@@ -3779,7 +3890,9 @@
         </is>
       </c>
       <c r="J54" s="13" t="n"/>
-      <c r="K54" s="14" t="inlineStr"/>
+      <c r="K54" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L54" s="13" t="n"/>
       <c r="M54" s="13" t="n"/>
       <c r="N54" s="13" t="n"/>
@@ -3830,7 +3943,9 @@
         </is>
       </c>
       <c r="J55" s="9" t="n"/>
-      <c r="K55" s="10" t="inlineStr"/>
+      <c r="K55" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L55" s="9" t="n"/>
       <c r="M55" s="9" t="n"/>
       <c r="N55" s="9" t="n"/>
@@ -3881,7 +3996,9 @@
         </is>
       </c>
       <c r="J56" s="13" t="n"/>
-      <c r="K56" s="14" t="inlineStr"/>
+      <c r="K56" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L56" s="13" t="n"/>
       <c r="M56" s="13" t="n"/>
       <c r="N56" s="13" t="n"/>
@@ -3932,7 +4049,9 @@
         </is>
       </c>
       <c r="J57" s="9" t="n"/>
-      <c r="K57" s="10" t="inlineStr"/>
+      <c r="K57" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L57" s="9" t="n"/>
       <c r="M57" s="9" t="n"/>
       <c r="N57" s="9" t="n"/>
@@ -3983,7 +4102,9 @@
         </is>
       </c>
       <c r="J58" s="13" t="n"/>
-      <c r="K58" s="14" t="inlineStr"/>
+      <c r="K58" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L58" s="13" t="n"/>
       <c r="M58" s="13" t="n"/>
       <c r="N58" s="13" t="n"/>
@@ -4034,7 +4155,9 @@
         </is>
       </c>
       <c r="J59" s="9" t="n"/>
-      <c r="K59" s="10" t="inlineStr"/>
+      <c r="K59" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L59" s="9" t="n"/>
       <c r="M59" s="9" t="n"/>
       <c r="N59" s="9" t="n"/>
@@ -4085,7 +4208,9 @@
         </is>
       </c>
       <c r="J60" s="13" t="n"/>
-      <c r="K60" s="14" t="inlineStr"/>
+      <c r="K60" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L60" s="13" t="n"/>
       <c r="M60" s="13" t="n"/>
       <c r="N60" s="13" t="n"/>
@@ -4136,7 +4261,9 @@
         </is>
       </c>
       <c r="J61" s="9" t="n"/>
-      <c r="K61" s="10" t="inlineStr"/>
+      <c r="K61" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L61" s="9" t="n"/>
       <c r="M61" s="9" t="n"/>
       <c r="N61" s="9" t="n"/>
@@ -4187,7 +4314,9 @@
         </is>
       </c>
       <c r="J62" s="13" t="n"/>
-      <c r="K62" s="14" t="inlineStr"/>
+      <c r="K62" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L62" s="13" t="n"/>
       <c r="M62" s="13" t="n"/>
       <c r="N62" s="13" t="n"/>
@@ -4238,7 +4367,9 @@
         </is>
       </c>
       <c r="J63" s="9" t="n"/>
-      <c r="K63" s="10" t="inlineStr"/>
+      <c r="K63" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L63" s="9" t="n"/>
       <c r="M63" s="9" t="n"/>
       <c r="N63" s="9" t="n"/>
@@ -4289,7 +4420,9 @@
         </is>
       </c>
       <c r="J64" s="13" t="n"/>
-      <c r="K64" s="14" t="inlineStr"/>
+      <c r="K64" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L64" s="13" t="n"/>
       <c r="M64" s="13" t="n"/>
       <c r="N64" s="13" t="n"/>
@@ -4340,7 +4473,9 @@
         </is>
       </c>
       <c r="J65" s="9" t="n"/>
-      <c r="K65" s="10" t="inlineStr"/>
+      <c r="K65" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L65" s="9" t="n"/>
       <c r="M65" s="9" t="n"/>
       <c r="N65" s="9" t="n"/>
@@ -4391,7 +4526,9 @@
         </is>
       </c>
       <c r="J66" s="13" t="n"/>
-      <c r="K66" s="14" t="inlineStr"/>
+      <c r="K66" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L66" s="13" t="n"/>
       <c r="M66" s="13" t="n"/>
       <c r="N66" s="13" t="n"/>
@@ -4442,7 +4579,9 @@
         </is>
       </c>
       <c r="J67" s="9" t="n"/>
-      <c r="K67" s="10" t="inlineStr"/>
+      <c r="K67" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L67" s="9" t="n"/>
       <c r="M67" s="9" t="n"/>
       <c r="N67" s="9" t="n"/>
@@ -4493,7 +4632,9 @@
         </is>
       </c>
       <c r="J68" s="13" t="n"/>
-      <c r="K68" s="14" t="inlineStr"/>
+      <c r="K68" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L68" s="13" t="n"/>
       <c r="M68" s="13" t="n"/>
       <c r="N68" s="13" t="n"/>
@@ -4544,7 +4685,9 @@
         </is>
       </c>
       <c r="J69" s="9" t="n"/>
-      <c r="K69" s="10" t="inlineStr"/>
+      <c r="K69" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L69" s="9" t="n"/>
       <c r="M69" s="9" t="n"/>
       <c r="N69" s="9" t="n"/>
@@ -4595,7 +4738,9 @@
         </is>
       </c>
       <c r="J70" s="13" t="n"/>
-      <c r="K70" s="14" t="inlineStr"/>
+      <c r="K70" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L70" s="13" t="n"/>
       <c r="M70" s="13" t="n"/>
       <c r="N70" s="13" t="n"/>
@@ -4646,7 +4791,9 @@
         </is>
       </c>
       <c r="J71" s="9" t="n"/>
-      <c r="K71" s="10" t="inlineStr"/>
+      <c r="K71" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L71" s="9" t="n"/>
       <c r="M71" s="9" t="n"/>
       <c r="N71" s="9" t="n"/>
@@ -4697,7 +4844,9 @@
         </is>
       </c>
       <c r="J72" s="13" t="n"/>
-      <c r="K72" s="14" t="inlineStr"/>
+      <c r="K72" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L72" s="13" t="n"/>
       <c r="M72" s="13" t="n"/>
       <c r="N72" s="13" t="n"/>
@@ -4748,7 +4897,9 @@
         </is>
       </c>
       <c r="J73" s="9" t="n"/>
-      <c r="K73" s="10" t="inlineStr"/>
+      <c r="K73" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L73" s="9" t="n"/>
       <c r="M73" s="9" t="n"/>
       <c r="N73" s="9" t="n"/>
@@ -4799,7 +4950,9 @@
         </is>
       </c>
       <c r="J74" s="13" t="n"/>
-      <c r="K74" s="14" t="inlineStr"/>
+      <c r="K74" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L74" s="13" t="n"/>
       <c r="M74" s="13" t="n"/>
       <c r="N74" s="13" t="n"/>
@@ -4850,7 +5003,9 @@
         </is>
       </c>
       <c r="J75" s="9" t="n"/>
-      <c r="K75" s="10" t="inlineStr"/>
+      <c r="K75" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L75" s="9" t="n"/>
       <c r="M75" s="9" t="n"/>
       <c r="N75" s="9" t="n"/>
@@ -4901,7 +5056,9 @@
         </is>
       </c>
       <c r="J76" s="13" t="n"/>
-      <c r="K76" s="14" t="inlineStr"/>
+      <c r="K76" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L76" s="13" t="n"/>
       <c r="M76" s="13" t="n"/>
       <c r="N76" s="13" t="n"/>
@@ -4952,7 +5109,9 @@
         </is>
       </c>
       <c r="J77" s="9" t="n"/>
-      <c r="K77" s="10" t="inlineStr"/>
+      <c r="K77" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L77" s="9" t="n"/>
       <c r="M77" s="9" t="n"/>
       <c r="N77" s="9" t="n"/>
@@ -5003,7 +5162,9 @@
         </is>
       </c>
       <c r="J78" s="13" t="n"/>
-      <c r="K78" s="14" t="inlineStr"/>
+      <c r="K78" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L78" s="13" t="n"/>
       <c r="M78" s="13" t="n"/>
       <c r="N78" s="13" t="n"/>
@@ -5054,7 +5215,9 @@
         </is>
       </c>
       <c r="J79" s="9" t="n"/>
-      <c r="K79" s="10" t="inlineStr"/>
+      <c r="K79" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L79" s="9" t="n"/>
       <c r="M79" s="9" t="n"/>
       <c r="N79" s="9" t="n"/>
@@ -5105,7 +5268,9 @@
         </is>
       </c>
       <c r="J80" s="13" t="n"/>
-      <c r="K80" s="14" t="inlineStr"/>
+      <c r="K80" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L80" s="13" t="n"/>
       <c r="M80" s="13" t="n"/>
       <c r="N80" s="13" t="n"/>
@@ -5156,7 +5321,9 @@
         </is>
       </c>
       <c r="J81" s="9" t="n"/>
-      <c r="K81" s="10" t="inlineStr"/>
+      <c r="K81" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L81" s="9" t="n"/>
       <c r="M81" s="9" t="n"/>
       <c r="N81" s="9" t="n"/>
@@ -5207,7 +5374,9 @@
         </is>
       </c>
       <c r="J82" s="13" t="n"/>
-      <c r="K82" s="14" t="inlineStr"/>
+      <c r="K82" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L82" s="13" t="n"/>
       <c r="M82" s="13" t="n"/>
       <c r="N82" s="13" t="n"/>
@@ -5258,7 +5427,9 @@
         </is>
       </c>
       <c r="J83" s="9" t="n"/>
-      <c r="K83" s="10" t="inlineStr"/>
+      <c r="K83" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L83" s="9" t="n"/>
       <c r="M83" s="9" t="n"/>
       <c r="N83" s="9" t="n"/>
@@ -5309,7 +5480,9 @@
         </is>
       </c>
       <c r="J84" s="13" t="n"/>
-      <c r="K84" s="14" t="inlineStr"/>
+      <c r="K84" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L84" s="13" t="n"/>
       <c r="M84" s="13" t="n"/>
       <c r="N84" s="13" t="n"/>
@@ -5360,7 +5533,9 @@
         </is>
       </c>
       <c r="J85" s="9" t="n"/>
-      <c r="K85" s="10" t="inlineStr"/>
+      <c r="K85" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L85" s="9" t="n"/>
       <c r="M85" s="9" t="n"/>
       <c r="N85" s="9" t="n"/>
@@ -5411,7 +5586,9 @@
         </is>
       </c>
       <c r="J86" s="13" t="n"/>
-      <c r="K86" s="14" t="inlineStr"/>
+      <c r="K86" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L86" s="13" t="n"/>
       <c r="M86" s="13" t="n"/>
       <c r="N86" s="13" t="n"/>
@@ -5462,7 +5639,9 @@
         </is>
       </c>
       <c r="J87" s="9" t="n"/>
-      <c r="K87" s="10" t="inlineStr"/>
+      <c r="K87" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L87" s="9" t="n"/>
       <c r="M87" s="9" t="n"/>
       <c r="N87" s="9" t="n"/>
@@ -5513,7 +5692,9 @@
         </is>
       </c>
       <c r="J88" s="13" t="n"/>
-      <c r="K88" s="14" t="inlineStr"/>
+      <c r="K88" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L88" s="13" t="n"/>
       <c r="M88" s="13" t="n"/>
       <c r="N88" s="13" t="n"/>
@@ -5564,7 +5745,9 @@
         </is>
       </c>
       <c r="J89" s="9" t="n"/>
-      <c r="K89" s="10" t="inlineStr"/>
+      <c r="K89" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L89" s="9" t="n"/>
       <c r="M89" s="9" t="n"/>
       <c r="N89" s="9" t="n"/>
@@ -5615,7 +5798,9 @@
         </is>
       </c>
       <c r="J90" s="13" t="n"/>
-      <c r="K90" s="14" t="inlineStr"/>
+      <c r="K90" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L90" s="13" t="n"/>
       <c r="M90" s="13" t="n"/>
       <c r="N90" s="13" t="n"/>
@@ -5666,7 +5851,9 @@
         </is>
       </c>
       <c r="J91" s="9" t="n"/>
-      <c r="K91" s="10" t="inlineStr"/>
+      <c r="K91" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L91" s="9" t="n"/>
       <c r="M91" s="9" t="n"/>
       <c r="N91" s="9" t="n"/>
@@ -5717,7 +5904,9 @@
         </is>
       </c>
       <c r="J92" s="13" t="n"/>
-      <c r="K92" s="14" t="inlineStr"/>
+      <c r="K92" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L92" s="13" t="n"/>
       <c r="M92" s="13" t="n"/>
       <c r="N92" s="13" t="n"/>
@@ -5768,7 +5957,9 @@
         </is>
       </c>
       <c r="J93" s="9" t="n"/>
-      <c r="K93" s="10" t="inlineStr"/>
+      <c r="K93" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L93" s="9" t="n"/>
       <c r="M93" s="9" t="n"/>
       <c r="N93" s="9" t="n"/>
@@ -5819,7 +6010,9 @@
         </is>
       </c>
       <c r="J94" s="13" t="n"/>
-      <c r="K94" s="14" t="inlineStr"/>
+      <c r="K94" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L94" s="13" t="n"/>
       <c r="M94" s="13" t="n"/>
       <c r="N94" s="13" t="n"/>
@@ -5870,7 +6063,9 @@
         </is>
       </c>
       <c r="J95" s="9" t="n"/>
-      <c r="K95" s="10" t="inlineStr"/>
+      <c r="K95" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L95" s="9" t="n"/>
       <c r="M95" s="9" t="n"/>
       <c r="N95" s="9" t="n"/>
@@ -5921,7 +6116,9 @@
         </is>
       </c>
       <c r="J96" s="13" t="n"/>
-      <c r="K96" s="14" t="inlineStr"/>
+      <c r="K96" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L96" s="13" t="n"/>
       <c r="M96" s="13" t="n"/>
       <c r="N96" s="13" t="n"/>
@@ -5972,7 +6169,9 @@
         </is>
       </c>
       <c r="J97" s="9" t="n"/>
-      <c r="K97" s="10" t="inlineStr"/>
+      <c r="K97" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L97" s="9" t="n"/>
       <c r="M97" s="9" t="n"/>
       <c r="N97" s="9" t="n"/>
@@ -6023,7 +6222,9 @@
         </is>
       </c>
       <c r="J98" s="13" t="n"/>
-      <c r="K98" s="14" t="inlineStr"/>
+      <c r="K98" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L98" s="13" t="n"/>
       <c r="M98" s="13" t="n"/>
       <c r="N98" s="13" t="n"/>
@@ -6074,7 +6275,9 @@
         </is>
       </c>
       <c r="J99" s="9" t="n"/>
-      <c r="K99" s="10" t="inlineStr"/>
+      <c r="K99" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L99" s="9" t="n"/>
       <c r="M99" s="9" t="n"/>
       <c r="N99" s="9" t="n"/>
@@ -6125,7 +6328,9 @@
         </is>
       </c>
       <c r="J100" s="13" t="n"/>
-      <c r="K100" s="14" t="inlineStr"/>
+      <c r="K100" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L100" s="13" t="n"/>
       <c r="M100" s="13" t="n"/>
       <c r="N100" s="13" t="n"/>
@@ -6176,7 +6381,9 @@
         </is>
       </c>
       <c r="J101" s="9" t="n"/>
-      <c r="K101" s="10" t="inlineStr"/>
+      <c r="K101" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L101" s="9" t="n"/>
       <c r="M101" s="9" t="n"/>
       <c r="N101" s="9" t="n"/>
@@ -6227,7 +6434,9 @@
         </is>
       </c>
       <c r="J102" s="13" t="n"/>
-      <c r="K102" s="14" t="inlineStr"/>
+      <c r="K102" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L102" s="13" t="n"/>
       <c r="M102" s="13" t="n"/>
       <c r="N102" s="13" t="n"/>
@@ -6278,7 +6487,9 @@
         </is>
       </c>
       <c r="J103" s="9" t="n"/>
-      <c r="K103" s="10" t="inlineStr"/>
+      <c r="K103" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L103" s="9" t="n"/>
       <c r="M103" s="9" t="n"/>
       <c r="N103" s="9" t="n"/>
@@ -6329,7 +6540,9 @@
         </is>
       </c>
       <c r="J104" s="13" t="n"/>
-      <c r="K104" s="14" t="inlineStr"/>
+      <c r="K104" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L104" s="13" t="n"/>
       <c r="M104" s="13" t="n"/>
       <c r="N104" s="13" t="n"/>
@@ -6380,7 +6593,9 @@
         </is>
       </c>
       <c r="J105" s="9" t="n"/>
-      <c r="K105" s="10" t="inlineStr"/>
+      <c r="K105" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L105" s="9" t="n"/>
       <c r="M105" s="9" t="n"/>
       <c r="N105" s="9" t="n"/>
@@ -6431,7 +6646,9 @@
         </is>
       </c>
       <c r="J106" s="13" t="n"/>
-      <c r="K106" s="14" t="inlineStr"/>
+      <c r="K106" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L106" s="13" t="n"/>
       <c r="M106" s="13" t="n"/>
       <c r="N106" s="13" t="n"/>
@@ -6482,7 +6699,9 @@
         </is>
       </c>
       <c r="J107" s="9" t="n"/>
-      <c r="K107" s="10" t="inlineStr"/>
+      <c r="K107" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L107" s="9" t="n"/>
       <c r="M107" s="9" t="n"/>
       <c r="N107" s="9" t="n"/>
@@ -6533,7 +6752,9 @@
         </is>
       </c>
       <c r="J108" s="13" t="n"/>
-      <c r="K108" s="14" t="inlineStr"/>
+      <c r="K108" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L108" s="13" t="n"/>
       <c r="M108" s="13" t="n"/>
       <c r="N108" s="13" t="n"/>
@@ -6580,7 +6801,9 @@
       </c>
       <c r="I109" s="8" t="inlineStr"/>
       <c r="J109" s="9" t="n"/>
-      <c r="K109" s="8" t="inlineStr"/>
+      <c r="K109" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="L109" s="9" t="n"/>
       <c r="M109" s="9" t="n"/>
       <c r="N109" s="9" t="n"/>
@@ -6619,7 +6842,9 @@
       <c r="H110" s="12" t="inlineStr"/>
       <c r="I110" s="12" t="inlineStr"/>
       <c r="J110" s="13" t="n"/>
-      <c r="K110" s="12" t="inlineStr"/>
+      <c r="K110" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="L110" s="13" t="n"/>
       <c r="M110" s="13" t="n"/>
       <c r="N110" s="13" t="n"/>

--- a/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_검사기팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_검사기팀_입력_2026.xlsx
@@ -214,7 +214,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -433,6 +433,24 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -554,15 +572,30 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <t>▣ NO (일련번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
+        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 관리코드 (프로젝트 고유 번호)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -576,46 +609,86 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 수주번호
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
+        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 고객사 (거래처명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
+        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 모델 (장비 모델명)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 모델 (장비 모델명)
 • 직접 입력 (좌측 정렬)
 • 예: SM-F776U PROXIMITY, IHVN-JG1
 • 고객사 제품 코드 또는 내부 모델명</t>
+        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
+        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <t>▣ PO유형 (발주 성격)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ PO유형 (발주 성격)
 • 드롭다운:
   신규 — 최초 수주 (신규 관리코드 채번)
   추가 — 기존 프로젝트 확장 (기존 코드 직접 입력)
@@ -626,11 +699,19 @@
   - 같은 검사기 단순 추가 발주: 기존 행에서 수량·금액 누적
   - 별도 추적 필요: 새 행 + 기존 관리코드 직접 입력
     (단 부서 진척률은 1개로 통합됨에 주의)</t>
+        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 영업단계 (Sales Pipeline)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 영업단계 (Sales Pipeline)
 • 드롭다운:
   제안작성 — 제안서 작성 중 (코드 미채번)
   제안제출 — 제안서 제출 완료 (코드 미채번)
@@ -645,31 +726,55 @@
   ④ 취소 — 납기일 순
   ※ 납품완료/완료는 4_완료이력으로 자동 이동
 💡 제안 단계는 관리코드 없이도 보존됨 (수주확정 전까지 추적)</t>
+        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 진행상태
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 진행상태
 • 드롭다운:
   수주예정 — 채번 전 대기 상태
   진행중 ★ — 작업 진행 중 (정렬 최상단)
   납품완료 — 완료 → 4_완료이력 자동 이관
   취소    — 수주 취소
   보류    — 일시 중단</t>
+        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서 담당자
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서 담당자
 • 부서 내 실제 담당자 이름 입력
   예: 정민규, 한재운, 이찬
 • 입력 시: PMS에도 자동 반영
 • 빈 칸: 부서 참여 확정, 담당자 미정</t>
+        </r>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서 진척률 (%) — 본인 부서 작업
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서 진척률 (%) — 본인 부서 작업
 • 자동 계산 (수정 불가, sync 시 갱신)
 • 시작일·완료일 입력 기반:
     0%  = 미착수    (시작일·완료일 모두 빈 칸)
@@ -678,11 +783,19 @@
 • ★ 이 값은 '이 부서'만의 진척률입니다.
 • 프로젝트 전체 진척률은 PMS 1_프로젝트등록
   '진척률(%)' 컬럼에서 확인 (= 완료부서/참여부서)</t>
+        </r>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서 시작일
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서 시작일
 ★ 날짜 입력 (% 아님 ⚠️)
 • 형식: YYYY-MM-DD  예: 2026-05-10
 • 허용: 26-5-10, 260510, 2026.5.10 (자동 정규화)
@@ -691,11 +804,19 @@
 • 비워두면: 미착수 상태
 • v3.1 검사기 운영: 진척률 % 대신 시작·완료일로 추적
   (2주 단위 빠른 작업 사이클이라 % 입력이 비효율)</t>
+        </r>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서 완료일
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서 완료일
 ★ 날짜 입력 (% 아님 ⚠️)
 • 형식: YYYY-MM-DD  예: 2026-05-24
 • 허용: 26-5-24, 260524, 2026.5.24 (자동 정규화)
@@ -705,28 +826,45 @@
 • 입력 시: PMS 2_진행현황에 자동 표시 +
   전체 진척률 = (완료 부서 수) / (참여 부서 수) 자동 계산
 • '제외' 부서는 분모에서 제외됨</t>
+        </r>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 부서 작업 상태
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 부서 작업 상태
 • 드롭다운 선택:
   미착수 — 작업 시작 안 함
   진행중 — 작업 진행 중
   완료   — 부서 작업 완료
   N/A    — 해당 부서 무관 프로젝트
 • 부서장이 매주 상태 갱신 권장</t>
+        </r>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>▣ 메모 (부서 자유 입력)
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>▣ 메모 (부서 자유 입력)
 • 자유 텍스트 입력
 • 활용:
   - 이슈사항 (예: 자재 결품, 외주 지연)
   - 변경 요청 (예: 사양 변경, 납기 조정)
   - 다른 부서·PM에게 공유할 정보
 • 대시보드 집계에는 미포함</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -1047,7 +1185,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="82" t="inlineStr">
+      <c r="A1" s="88" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 검사기팀 │ 2026</t>
         </is>
@@ -1068,7 +1206,7 @@
       <c r="O1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="83" t="inlineStr">
+      <c r="A2" s="89" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 검사기팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1086,9 +1224,9 @@
       <c r="L2" s="16" t="n"/>
       <c r="M2" s="16" t="n"/>
       <c r="N2" s="17" t="n"/>
-      <c r="O2" s="84" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 11:44</t>
+      <c r="O2" s="90" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 12:33</t>
         </is>
       </c>
     </row>

--- a/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_검사기팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_검사기팀_입력_2026.xlsx
@@ -130,7 +130,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -210,11 +210,40 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -488,6 +517,17 @@
     <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1185,7 +1225,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="88" t="inlineStr">
+      <c r="A1" s="91" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 검사기팀 │ 2026</t>
         </is>
@@ -1206,7 +1246,7 @@
       <c r="O1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="89" t="inlineStr">
+      <c r="A2" s="92" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 검사기팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1221,14 +1261,14 @@
       <c r="I2" s="16" t="n"/>
       <c r="J2" s="16" t="n"/>
       <c r="K2" s="16" t="n"/>
-      <c r="L2" s="16" t="n"/>
-      <c r="M2" s="16" t="n"/>
-      <c r="N2" s="17" t="n"/>
-      <c r="O2" s="90" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 12:33</t>
-        </is>
-      </c>
+      <c r="L2" s="17" t="n"/>
+      <c r="M2" s="93" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 12:58</t>
+        </is>
+      </c>
+      <c r="N2" s="94" t="n"/>
+      <c r="O2" s="95" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -7500,9 +7540,10 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0" password="DEDA"/>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="M2:O2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="Q5:Q109" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="입력 오류" error="목록에서 선택하세요" type="list">

--- a/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_검사기팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_검사기팀_입력_2026.xlsx
@@ -243,7 +243,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -528,6 +528,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -841,7 +850,10 @@
 • 허용: 26-5-10, 260510, 2026.5.10 (자동 정규화)
 • 부서가 ★실제로 작업을 시작한 날짜★ 기입
 • PO 후 작업 착수일 (지시 받은 날 아님)
-• 비워두면: 미착수 상태
+📋 입력값 의미:
+  ▸ 빈 칸 → 미착수 또는 '해당없음'
+           (부서 자체가 해당없음이면 PMS에서 '제외' 선택 권장)
+  ▸ 날짜 → 시작 (부서 진척률 50% 인식)
 • v3.1 검사기 운영: 진척률 % 대신 시작·완료일로 추적
   (2주 단위 빠른 작업 사이클이라 % 입력이 비효율)</t>
         </r>
@@ -862,7 +874,10 @@
 • 허용: 26-5-24, 260524, 2026.5.24 (자동 정규화)
 • 부서 작업이 ★실제로 완료된 날짜★ 기입
 • 예정일 아닌 ★실제 완료일★ 만 입력
-• 비워두면: PMS 진행현황에서 '미완료'로 집계
+📋 입력값 의미:
+  ▸ 빈 칸 → 미완료 또는 '해당없음'
+           (부서 자체가 해당없음이면 PMS에서 '제외' 선택 권장)
+  ▸ 날짜 → 완료 (부서 진척률 100%)
 • 입력 시: PMS 2_진행현황에 자동 표시 +
   전체 진척률 = (완료 부서 수) / (참여 부서 수) 자동 계산
 • '제외' 부서는 분모에서 제외됨</t>
@@ -1215,8 +1230,8 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" style="43" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" style="43" min="12" max="12"/>
-    <col width="12" customWidth="1" style="43" min="13" max="13"/>
+    <col width="5" customWidth="1" style="43" min="12" max="12"/>
+    <col width="5" customWidth="1" style="43" min="13" max="13"/>
     <col width="10" customWidth="1" style="43" min="14" max="14"/>
     <col width="28" customWidth="1" style="43" min="15" max="15"/>
     <col width="10" customWidth="1" style="43" min="16" max="16"/>
@@ -1225,7 +1240,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="91" t="inlineStr">
+      <c r="A1" s="96" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 검사기팀 │ 2026</t>
         </is>
@@ -1246,7 +1261,7 @@
       <c r="O1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="92" t="inlineStr">
+      <c r="A2" s="97" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 검사기팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1262,13 +1277,13 @@
       <c r="J2" s="16" t="n"/>
       <c r="K2" s="16" t="n"/>
       <c r="L2" s="17" t="n"/>
-      <c r="M2" s="93" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 12:58</t>
-        </is>
-      </c>
-      <c r="N2" s="94" t="n"/>
-      <c r="O2" s="95" t="n"/>
+      <c r="M2" s="98" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:26</t>
+        </is>
+      </c>
+      <c r="N2" s="16" t="n"/>
+      <c r="O2" s="17" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">

--- a/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_검사기팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_검사기팀_입력_2026.xlsx
@@ -243,7 +243,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -528,6 +528,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -1230,8 +1239,8 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" style="43" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="5" customWidth="1" style="43" min="12" max="12"/>
-    <col width="5" customWidth="1" style="43" min="13" max="13"/>
+    <col width="7" customWidth="1" style="43" min="12" max="12"/>
+    <col width="7" customWidth="1" style="43" min="13" max="13"/>
     <col width="10" customWidth="1" style="43" min="14" max="14"/>
     <col width="28" customWidth="1" style="43" min="15" max="15"/>
     <col width="10" customWidth="1" style="43" min="16" max="16"/>
@@ -1240,7 +1249,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="96" t="inlineStr">
+      <c r="A1" s="99" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 검사기팀 │ 2026</t>
         </is>
@@ -1261,7 +1270,7 @@
       <c r="O1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="97" t="inlineStr">
+      <c r="A2" s="100" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 검사기팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1277,9 +1286,9 @@
       <c r="J2" s="16" t="n"/>
       <c r="K2" s="16" t="n"/>
       <c r="L2" s="17" t="n"/>
-      <c r="M2" s="98" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:26</t>
+      <c r="M2" s="101" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:38</t>
         </is>
       </c>
       <c r="N2" s="16" t="n"/>

--- a/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_검사기팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_검사기팀_입력_2026.xlsx
@@ -243,7 +243,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -528,6 +528,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -1249,7 +1258,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="99" t="inlineStr">
+      <c r="A1" s="102" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 검사기팀 │ 2026</t>
         </is>
@@ -1270,7 +1279,7 @@
       <c r="O1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="100" t="inlineStr">
+      <c r="A2" s="103" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 검사기팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1286,9 +1295,9 @@
       <c r="J2" s="16" t="n"/>
       <c r="K2" s="16" t="n"/>
       <c r="L2" s="17" t="n"/>
-      <c r="M2" s="101" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:38</t>
+      <c r="M2" s="104" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:46</t>
         </is>
       </c>
       <c r="N2" s="16" t="n"/>

--- a/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_검사기팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_검사기팀_입력_2026.xlsx
@@ -243,7 +243,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -528,6 +528,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -1258,7 +1267,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="102" t="inlineStr">
+      <c r="A1" s="105" t="inlineStr">
         <is>
           <t>㈜케이엔케이 │ 검사기_완제품 │ 검사기팀 │ 2026</t>
         </is>
@@ -1279,7 +1288,7 @@
       <c r="O1" s="17" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="103" t="inlineStr">
+      <c r="A2" s="106" t="inlineStr">
         <is>
           <t>㈜케이엔케이  |  검사기 검사기팀 전용  |  HAIST Innovation  |  Human &amp; AI create the Best</t>
         </is>
@@ -1295,9 +1304,9 @@
       <c r="J2" s="16" t="n"/>
       <c r="K2" s="16" t="n"/>
       <c r="L2" s="17" t="n"/>
-      <c r="M2" s="104" t="inlineStr">
-        <is>
-          <t>업데이트: 2026-05-03 13:46</t>
+      <c r="M2" s="107" t="inlineStr">
+        <is>
+          <t>업데이트: 2026-05-03 13:58</t>
         </is>
       </c>
       <c r="N2" s="16" t="n"/>

--- a/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_검사기팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V3/01_검사기_완제품/KNK_검사기_완제품_검사기팀_입력_2026.xlsx
@@ -648,30 +648,15 @@
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ NO (일련번호)
+        <t>▣ NO (일련번호)
 • sync 실행 시 1부터 자동 채번
 • 정렬 후 번호 재부여 (수동 입력 불가)
 • 최상단이 가장 납기 임박한 진행중 건</t>
-        </r>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 관리코드 (프로젝트 고유 번호)
+        <t>▣ 관리코드 (프로젝트 고유 번호)
 • 포맷: [SEQ 3자리][사업부][YYMM]  예: 001T2604
   - 사업부 T=검사기, M=자동화
   - YYMM = 채번 시점 연월
@@ -685,86 +670,46 @@
   진척률·진행상태는 행마다 별도 관리되나
   부서 입력 파일에서는 1개로 통합됨 (마지막 행 기준)
   → 가급적 한 관리코드는 한 행으로 운영 권장</t>
-        </r>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 수주번호
+        <t>▣ 수주번호
 • 포맷: [사업부]-[수주일 YYMMDD]  예: T-260501
 • 동일 수주일 복수 건: 뒤에 -N  예: T-260501-2
 • 관리코드가 채번된 후 자동 생성
   - C17 수주일이 비어있으면 오늘 날짜로 부여
   - 정확한 수주일 입력 후 .bat 실행 권장
 • R3=🔒자동 (사용자 수정 비권장 — sync 시 일관성 유지)</t>
-        </r>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 고객사 (거래처명)
+        <t>▣ 고객사 (거래처명)
 • 직접 입력 — 고객사 회사명
 • 예: 삼성전자, 드림텍, 파인텍, KNK VINA(삼성전자)
 • 대시보드 고객사별 매출 집계 기준</t>
-        </r>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 모델 (장비 모델명)
+        <t>▣ 모델 (장비 모델명)
 • 직접 입력 (좌측 정렬)
 • 예: SM-F776U PROXIMITY, IHVN-JG1
 • 고객사 제품 코드 또는 내부 모델명</t>
-        </r>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 품명 (장비 명칭 / 작업 내용)
+        <t>▣ 품명 (장비 명칭 / 작업 내용)
 • 직접 입력 (좌측 정렬)
 • 예: 기능검사기 MODIFY, ASSY 검사기
 • 서술적 이름 — 경영진이 한눈에 이해 가능하게</t>
-        </r>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ PO유형 (발주 성격)
+        <t>▣ PO유형 (발주 성격)
 • 드롭다운:
   신규 — 최초 수주 (신규 관리코드 채번)
   추가 — 기존 프로젝트 확장 (기존 코드 직접 입력)
@@ -775,19 +720,11 @@
   - 같은 검사기 단순 추가 발주: 기존 행에서 수량·금액 누적
   - 별도 추적 필요: 새 행 + 기존 관리코드 직접 입력
     (단 부서 진척률은 1개로 통합됨에 주의)</t>
-        </r>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 영업단계 (Sales Pipeline)
+        <t>▣ 영업단계 (Sales Pipeline)
 • 드롭다운:
   제안작성 — 제안서 작성 중 (코드 미채번)
   제안제출 — 제안서 제출 완료 (코드 미채번)
@@ -802,55 +739,31 @@
   ④ 취소 — 납기일 순
   ※ 납품완료/완료는 4_완료이력으로 자동 이동
 💡 제안 단계는 관리코드 없이도 보존됨 (수주확정 전까지 추적)</t>
-        </r>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 진행상태
+        <t>▣ 진행상태
 • 드롭다운:
   수주예정 — 채번 전 대기 상태
   진행중 ★ — 작업 진행 중 (정렬 최상단)
   납품완료 — 완료 → 4_완료이력 자동 이관
   취소    — 수주 취소
   보류    — 일시 중단</t>
-        </r>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서 담당자
+        <t>▣ 부서 담당자
 • 부서 내 실제 담당자 이름 입력
   예: 정민규, 한재운, 이찬
 • 입력 시: PMS에도 자동 반영
 • 빈 칸: 부서 참여 확정, 담당자 미정</t>
-        </r>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서 진척률 (%) — 본인 부서 작업
+        <t>▣ 부서 진척률 (%) — 본인 부서 작업
 • 자동 계산 (수정 불가, sync 시 갱신)
 • 시작일·완료일 입력 기반:
     0%  = 미착수    (시작일·완료일 모두 빈 칸)
@@ -859,19 +772,11 @@
 • ★ 이 값은 '이 부서'만의 진척률입니다.
 • 프로젝트 전체 진척률은 PMS 1_프로젝트등록
   '진척률(%)' 컬럼에서 확인 (= 완료부서/참여부서)</t>
-        </r>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서 시작일
+        <t>▣ 부서 시작일
 ★ 날짜 입력 (% 아님 ⚠️)
 • 형식: YYYY-MM-DD  예: 2026-05-10
 • 허용: 26-5-10, 260510, 2026.5.10 (자동 정규화)
@@ -883,19 +788,11 @@
   ▸ 날짜 → 시작 (부서 진척률 50% 인식)
 • v3.1 검사기 운영: 진척률 % 대신 시작·완료일로 추적
   (2주 단위 빠른 작업 사이클이라 % 입력이 비효율)</t>
-        </r>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서 완료일
+        <t>▣ 부서 완료일
 ★ 날짜 입력 (% 아님 ⚠️)
 • 형식: YYYY-MM-DD  예: 2026-05-24
 • 허용: 26-5-24, 260524, 2026.5.24 (자동 정규화)
@@ -908,45 +805,28 @@
 • 입력 시: PMS 2_진행현황에 자동 표시 +
   전체 진척률 = (완료 부서 수) / (참여 부서 수) 자동 계산
 • '제외' 부서는 분모에서 제외됨</t>
-        </r>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 부서 작업 상태
+        <t>▣ 부서 작업 상태
 • 드롭다운 선택:
   미착수 — 작업 시작 안 함
   진행중 — 작업 진행 중
   완료   — 부서 작업 완료
   N/A    — 해당 부서 무관 프로젝트
 • 부서장이 매주 상태 갱신 권장</t>
-        </r>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <rFont val="맑은 고딕"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>▣ 메모 (부서 자유 입력)
+        <t>▣ 메모 (부서 자유 입력)
 • 자유 텍스트 입력
 • 활용:
   - 이슈사항 (예: 자재 결품, 외주 지연)
   - 변경 요청 (예: 사양 변경, 납기 조정)
   - 다른 부서·PM에게 공유할 정보
 • 대시보드 집계에는 미포함</t>
-        </r>
       </text>
     </comment>
   </commentList>
@@ -1479,7 +1359,7 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>T-260407-3</t>
+          <t>T-260407-2</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
@@ -1585,7 +1465,7 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>T-260303-2</t>
+          <t>T-260303-1</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
@@ -1691,7 +1571,7 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>T-260409-2</t>
+          <t>T-260409-1</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
@@ -1744,7 +1624,7 @@
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>T-260409-3</t>
+          <t>T-260409-2</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
@@ -1797,7 +1677,7 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>T-260410-2</t>
+          <t>T-260410-1</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
@@ -1850,7 +1730,7 @@
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>T-260410-3</t>
+          <t>T-260410-2</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
@@ -1903,7 +1783,7 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>T-260403-6</t>
+          <t>T-260403-5</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
@@ -1956,7 +1836,7 @@
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>T-260408-7</t>
+          <t>T-260408-6</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
@@ -2009,7 +1889,7 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>T-260408-8</t>
+          <t>T-260408-7</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
@@ -2062,7 +1942,7 @@
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>T-260408-9</t>
+          <t>T-260408-8</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
@@ -2115,7 +1995,7 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>T-260408-10</t>
+          <t>T-260408-9</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
@@ -2168,7 +2048,7 @@
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>T-260406-2</t>
+          <t>T-260406-1</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
@@ -2221,7 +2101,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>T-260406-3</t>
+          <t>T-260406-2</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
@@ -2274,7 +2154,7 @@
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>T-260406-4</t>
+          <t>T-260406-3</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
@@ -2327,7 +2207,7 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>T-260406-5</t>
+          <t>T-260406-4</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
@@ -2380,7 +2260,7 @@
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>T-260406-6</t>
+          <t>T-260406-5</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
@@ -2433,7 +2313,7 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>T-260406-7</t>
+          <t>T-260406-6</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
@@ -2486,7 +2366,7 @@
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>T-260406-12</t>
+          <t>T-260406-11</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
@@ -2539,7 +2419,7 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>T-260406-13</t>
+          <t>T-260406-12</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
@@ -2592,7 +2472,7 @@
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>T-260406-14</t>
+          <t>T-260406-13</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
@@ -2645,7 +2525,7 @@
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>T-260406-15</t>
+          <t>T-260406-14</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
@@ -2804,7 +2684,7 @@
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>T-260327-2</t>
+          <t>T-260327-1</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
@@ -2857,7 +2737,7 @@
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>T-260327-3</t>
+          <t>T-260327-2</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
@@ -2910,7 +2790,7 @@
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>T-260327-4</t>
+          <t>T-260327-3</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
@@ -2963,7 +2843,7 @@
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>T-260327-5</t>
+          <t>T-260327-4</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
@@ -3016,7 +2896,7 @@
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>T-260327-6</t>
+          <t>T-260327-5</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
@@ -3069,7 +2949,7 @@
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>T-260327-7</t>
+          <t>T-260327-6</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
@@ -3175,7 +3055,7 @@
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>T-260331-2</t>
+          <t>T-260331-1</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
@@ -3228,7 +3108,7 @@
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>T-260324-5</t>
+          <t>T-260324-4</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
@@ -3281,7 +3161,7 @@
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>T-260401-4</t>
+          <t>T-260401-3</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
@@ -3440,7 +3320,7 @@
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>T-260323-2</t>
+          <t>T-260323-1</t>
         </is>
       </c>
       <c r="D42" s="12" t="inlineStr">
@@ -3493,7 +3373,7 @@
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>T-260323-3</t>
+          <t>T-260323-2</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
@@ -3546,7 +3426,7 @@
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>T-260323-4</t>
+          <t>T-260323-3</t>
         </is>
       </c>
       <c r="D44" s="12" t="inlineStr">
@@ -3599,7 +3479,7 @@
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>T-260323-5</t>
+          <t>T-260323-4</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
@@ -3652,7 +3532,7 @@
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>T-260323-6</t>
+          <t>T-260323-5</t>
         </is>
       </c>
       <c r="D46" s="12" t="inlineStr">
@@ -3705,7 +3585,7 @@
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>T-260406-16</t>
+          <t>T-260406-15</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
@@ -3811,7 +3691,7 @@
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>T-260408-2</t>
+          <t>T-260408-1</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
@@ -3864,7 +3744,7 @@
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>T-260408-3</t>
+          <t>T-260408-2</t>
         </is>
       </c>
       <c r="D50" s="12" t="inlineStr">
@@ -3917,7 +3797,7 @@
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>T-260408-4</t>
+          <t>T-260408-3</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
@@ -3970,7 +3850,7 @@
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>T-260406-8</t>
+          <t>T-260406-7</t>
         </is>
       </c>
       <c r="D52" s="12" t="inlineStr">
@@ -4023,7 +3903,7 @@
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>T-260406-9</t>
+          <t>T-260406-8</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
@@ -4076,7 +3956,7 @@
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>T-260406-10</t>
+          <t>T-260406-9</t>
         </is>
       </c>
       <c r="D54" s="12" t="inlineStr">
@@ -4129,7 +4009,7 @@
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>T-260406-11</t>
+          <t>T-260406-10</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
@@ -4182,7 +4062,7 @@
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>T-260407-2</t>
+          <t>T-260407-1</t>
         </is>
       </c>
       <c r="D56" s="12" t="inlineStr">
@@ -4235,7 +4115,7 @@
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>T-260409-4</t>
+          <t>T-260409-3</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
@@ -4288,7 +4168,7 @@
       </c>
       <c r="C58" s="12" t="inlineStr">
         <is>
-          <t>T-260409-5</t>
+          <t>T-260409-4</t>
         </is>
       </c>
       <c r="D58" s="12" t="inlineStr">
@@ -4341,7 +4221,7 @@
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>T-260409-6</t>
+          <t>T-260409-5</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
@@ -4447,7 +4327,7 @@
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>T-260324-8</t>
+          <t>T-260324-7</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
@@ -4500,7 +4380,7 @@
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>T-260407-4</t>
+          <t>T-260407-3</t>
         </is>
       </c>
       <c r="D62" s="12" t="inlineStr">
@@ -4553,7 +4433,7 @@
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>T-260324-10</t>
+          <t>T-260324-9</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
@@ -4606,7 +4486,7 @@
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>T-260410-4</t>
+          <t>T-260410-3</t>
         </is>
       </c>
       <c r="D64" s="12" t="inlineStr">
@@ -4712,7 +4592,7 @@
       </c>
       <c r="C66" s="12" t="inlineStr">
         <is>
-          <t>T-260413-2</t>
+          <t>T-260413-1</t>
         </is>
       </c>
       <c r="D66" s="12" t="inlineStr">
@@ -4765,7 +4645,7 @@
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>T-260413-3</t>
+          <t>T-260413-2</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
@@ -4818,7 +4698,7 @@
       </c>
       <c r="C68" s="12" t="inlineStr">
         <is>
-          <t>T-260413-4</t>
+          <t>T-260413-3</t>
         </is>
       </c>
       <c r="D68" s="12" t="inlineStr">
@@ -4871,7 +4751,7 @@
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>T-260413-5</t>
+          <t>T-260413-4</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
@@ -4924,7 +4804,7 @@
       </c>
       <c r="C70" s="12" t="inlineStr">
         <is>
-          <t>T-260409-7</t>
+          <t>T-260409-6</t>
         </is>
       </c>
       <c r="D70" s="12" t="inlineStr">
@@ -4977,7 +4857,7 @@
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>T-260409-8</t>
+          <t>T-260409-7</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
@@ -5030,7 +4910,7 @@
       </c>
       <c r="C72" s="12" t="inlineStr">
         <is>
-          <t>T-260409-9</t>
+          <t>T-260409-8</t>
         </is>
       </c>
       <c r="D72" s="12" t="inlineStr">
@@ -5083,7 +4963,7 @@
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>T-260409-10</t>
+          <t>T-260409-9</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
@@ -5136,7 +5016,7 @@
       </c>
       <c r="C74" s="12" t="inlineStr">
         <is>
-          <t>T-260409-11</t>
+          <t>T-260409-10</t>
         </is>
       </c>
       <c r="D74" s="12" t="inlineStr">
@@ -5242,7 +5122,7 @@
       </c>
       <c r="C76" s="12" t="inlineStr">
         <is>
-          <t>T-260407-5</t>
+          <t>T-260407-4</t>
         </is>
       </c>
       <c r="D76" s="12" t="inlineStr">
@@ -5295,7 +5175,7 @@
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>T-260413-6</t>
+          <t>T-260413-5</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
@@ -5348,7 +5228,7 @@
       </c>
       <c r="C78" s="12" t="inlineStr">
         <is>
-          <t>T-260413-7</t>
+          <t>T-260413-6</t>
         </is>
       </c>
       <c r="D78" s="12" t="inlineStr">
@@ -5401,7 +5281,7 @@
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>T-260413-8</t>
+          <t>T-260413-7</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
@@ -5454,7 +5334,7 @@
       </c>
       <c r="C80" s="12" t="inlineStr">
         <is>
-          <t>T-260413-9</t>
+          <t>T-260413-8</t>
         </is>
       </c>
       <c r="D80" s="12" t="inlineStr">
@@ -5507,7 +5387,7 @@
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>T-260413-10</t>
+          <t>T-260413-9</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
@@ -5560,7 +5440,7 @@
       </c>
       <c r="C82" s="12" t="inlineStr">
         <is>
-          <t>T-260413-11</t>
+          <t>T-260413-10</t>
         </is>
       </c>
       <c r="D82" s="12" t="inlineStr">
@@ -5613,7 +5493,7 @@
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>T-260331-3</t>
+          <t>T-260331-2</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
@@ -5772,7 +5652,7 @@
       </c>
       <c r="C86" s="12" t="inlineStr">
         <is>
-          <t>T-260324-9</t>
+          <t>T-260324-8</t>
         </is>
       </c>
       <c r="D86" s="12" t="inlineStr">
@@ -5825,7 +5705,7 @@
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>T-260413-12</t>
+          <t>T-260413-11</t>
         </is>
       </c>
       <c r="D87" s="8" t="inlineStr">
@@ -5878,7 +5758,7 @@
       </c>
       <c r="C88" s="12" t="inlineStr">
         <is>
-          <t>T-260413-17</t>
+          <t>T-260413-16</t>
         </is>
       </c>
       <c r="D88" s="12" t="inlineStr">
@@ -5931,7 +5811,7 @@
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>T-260413-18</t>
+          <t>T-260413-17</t>
         </is>
       </c>
       <c r="D89" s="8" t="inlineStr">
@@ -5984,7 +5864,7 @@
       </c>
       <c r="C90" s="12" t="inlineStr">
         <is>
-          <t>T-260413-19</t>
+          <t>T-260413-18</t>
         </is>
       </c>
       <c r="D90" s="12" t="inlineStr">
@@ -6090,7 +5970,7 @@
       </c>
       <c r="C92" s="12" t="inlineStr">
         <is>
-          <t>T-260415-2</t>
+          <t>T-260415-1</t>
         </is>
       </c>
       <c r="D92" s="12" t="inlineStr">
@@ -6143,7 +6023,7 @@
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t>T-260415-3</t>
+          <t>T-260415-2</t>
         </is>
       </c>
       <c r="D93" s="8" t="inlineStr">
@@ -6196,7 +6076,7 @@
       </c>
       <c r="C94" s="12" t="inlineStr">
         <is>
-          <t>T-260413-13</t>
+          <t>T-260413-12</t>
         </is>
       </c>
       <c r="D94" s="12" t="inlineStr">
@@ -6249,7 +6129,7 @@
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t>T-260413-14</t>
+          <t>T-260413-13</t>
         </is>
       </c>
       <c r="D95" s="8" t="inlineStr">
@@ -6302,7 +6182,7 @@
       </c>
       <c r="C96" s="12" t="inlineStr">
         <is>
-          <t>T-260413-15</t>
+          <t>T-260413-14</t>
         </is>
       </c>
       <c r="D96" s="12" t="inlineStr">
@@ -6355,7 +6235,7 @@
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>T-260413-16</t>
+          <t>T-260413-15</t>
         </is>
       </c>
       <c r="D97" s="8" t="inlineStr">
@@ -6408,7 +6288,7 @@
       </c>
       <c r="C98" s="12" t="inlineStr">
         <is>
-          <t>T-260408-5</t>
+          <t>T-260408-4</t>
         </is>
       </c>
       <c r="D98" s="12" t="inlineStr">
@@ -6461,7 +6341,7 @@
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t>T-260408-6</t>
+          <t>T-260408-5</t>
         </is>
       </c>
       <c r="D99" s="8" t="inlineStr">
@@ -6567,7 +6447,7 @@
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t>T-260414-2</t>
+          <t>T-260414-1</t>
         </is>
       </c>
       <c r="D101" s="8" t="inlineStr">
@@ -6620,7 +6500,7 @@
       </c>
       <c r="C102" s="12" t="inlineStr">
         <is>
-          <t>T-260413-20</t>
+          <t>T-260413-19</t>
         </is>
       </c>
       <c r="D102" s="12" t="inlineStr">
@@ -6673,7 +6553,7 @@
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t>T-260413-21</t>
+          <t>T-260413-20</t>
         </is>
       </c>
       <c r="D103" s="8" t="inlineStr">
@@ -6726,7 +6606,7 @@
       </c>
       <c r="C104" s="12" t="inlineStr">
         <is>
-          <t>T-260414-3</t>
+          <t>T-260414-2</t>
         </is>
       </c>
       <c r="D104" s="12" t="inlineStr">
@@ -6779,7 +6659,7 @@
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t>T-260226-2</t>
+          <t>T-260226-1</t>
         </is>
       </c>
       <c r="D105" s="8" t="inlineStr">
@@ -6832,7 +6712,7 @@
       </c>
       <c r="C106" s="12" t="inlineStr">
         <is>
-          <t>T-260226-3</t>
+          <t>T-260226-2</t>
         </is>
       </c>
       <c r="D106" s="12" t="inlineStr">
@@ -6938,7 +6818,7 @@
       </c>
       <c r="C108" s="12" t="inlineStr">
         <is>
-          <t>T-260331-12</t>
+          <t>T-260331-11</t>
         </is>
       </c>
       <c r="D108" s="12" t="inlineStr">
@@ -7040,7 +6920,7 @@
       </c>
       <c r="C110" s="12" t="inlineStr">
         <is>
-          <t>T-260425-2</t>
+          <t>T-260425-1</t>
         </is>
       </c>
       <c r="D110" s="12" t="inlineStr">
